--- a/docs/Master-Data-Sheets/cureka_category_page_descriptions_above the fold.xlsx
+++ b/docs/Master-Data-Sheets/cureka_category_page_descriptions_above the fold.xlsx
@@ -1,31 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
-    <sheet name="healthcare devices" sheetId="1" r:id="rId1"/>
-    <sheet name="Herbal &amp; Ayurvedha" sheetId="2" r:id="rId2"/>
-    <sheet name="vitamins &amp; nutrition" sheetId="3" r:id="rId3"/>
-    <sheet name="personal care" sheetId="4" r:id="rId4"/>
-    <sheet name="baby care" sheetId="5" r:id="rId5"/>
-    <sheet name="sexual wellness" sheetId="6" r:id="rId6"/>
-    <sheet name="women care" sheetId="7" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId8"/>
+    <sheet sheetId="1" name="healthcare devices" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Herbal &amp; Ayurvedha" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="vitamins &amp; nutrition" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="personal care" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="baby care" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="sexual wellness" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="women care" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Sheet1" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'baby care'!$A$1:$G$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'healthcare devices'!$A$1:$G$56</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Herbal &amp; Ayurvedha'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'personal care'!$A$1:$G$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'sexual wellness'!$A$1:$G$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'vitamins &amp; nutrition'!$A$1:$G$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'women care'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase">'women care'!$A$1:$G$21</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -194,7 +188,7 @@
     <t>smart bands</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/healthcare-devices/daily-living-aids/smart-wearables</t>
+    <t>https://beta.cureka.com/product-category/healthcare-devices/daily-living-aids/smart-bands</t>
   </si>
   <si>
     <t>smart fitness band</t>
@@ -710,7 +704,7 @@
     <t>nebulizer</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/healthcare-devices/medical-equipments/nebulizers-vaporizers</t>
+    <t>https://beta.cureka.com/product-category/healthcare-devices/medical-equipments/nebulizer</t>
   </si>
   <si>
     <t>nebulizer machine</t>
@@ -962,7 +956,7 @@
     <t>cerebral palsy</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/healthcare-devices/mobility-aids/cerebral-palsy</t>
+    <t>https://beta.cureka.com/product-category/healthcare-devices/mobility-aids/cerebral-palsy-special-aids</t>
   </si>
   <si>
     <t>cerebral palsy aids</t>
@@ -983,7 +977,7 @@
     <t>pain management</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/healthcare-devices/pain-management</t>
+    <t>https://beta.cureka.com/product-category/healthcare-devices/pain-relief</t>
   </si>
   <si>
     <t>pain relief</t>
@@ -1001,7 +995,7 @@
     <t>heating pads massager</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/healthcare-devices/pain-management/heating-pads-massager</t>
+    <t>https://beta.cureka.com/product-category/healthcare-devices/pain-relief/heating-pads-massager</t>
   </si>
   <si>
     <t>heating pad</t>
@@ -1022,7 +1016,7 @@
     <t>weight cuff</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/healthcare-devices/pain-management/weight-cuff</t>
+    <t>https://beta.cureka.com/product-category/healthcare-devices/pain-relief/weight-cuff</t>
   </si>
   <si>
     <t>ankle weights</t>
@@ -1040,7 +1034,7 @@
     <t>wound care dressings</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/healthcare-devices/pain-management/wound-care-dressings</t>
+    <t>https://beta.cureka.com/product-category/healthcare-devices/pain-relief/wound-care-dressings</t>
   </si>
   <si>
     <t>wound dressing</t>
@@ -1058,7 +1052,7 @@
     <t>hot cold pack</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/healthcare-devices/pain-management/hot-cold-pack</t>
+    <t>https://beta.cureka.com/product-category/healthcare-devices/pain-relief/hot-cold-pack</t>
   </si>
   <si>
     <t>hot and cold pack</t>
@@ -1076,7 +1070,7 @@
     <t>topical pain relief</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/healthcare-devices/pain-management/topical-pain-relief</t>
+    <t>https://beta.cureka.com/product-category/healthcare-devices/pain-relief/topical-pain-relief</t>
   </si>
   <si>
     <t>pain relief gel</t>
@@ -1190,10 +1184,13 @@
     <t>natural shampoo conditioner</t>
   </si>
   <si>
+    <t>Cureka keeps its herbal hair oil range doctor-curated for natural, preventive care, making every pick genuine and dependable. The range addresses concerns like hair fall, dandruff, and everyday hair care, with options such as naturals hair shampoo, herbal hair growth oil, and natural shampoo conditioner to explore. Gentle, natural care can be both effective and reassuring.</t>
+  </si>
+  <si>
     <t>Herbal Joint Care</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/herbal-ayurveda/herbal-care/herbal-joint-care-2</t>
+    <t>https://beta.cureka.com/product-category/herbal-ayurveda/herbal-care/herbal-joint-care</t>
   </si>
   <si>
     <t>herbal joint care</t>
@@ -1208,6 +1205,9 @@
     <t>joint care products</t>
   </si>
   <si>
+    <t>Cureka’s herbal joint care range is doctor-curated for natural, preventive care, with authenticity you can count on. Designed to support concerns like joint stiffness, discomfort, and everyday mobility, the collection includes joint support medicine, natural joint support supplements, and trusted joint care products to explore. Thoughtfully sourced ingredients make natural joint care a dependable choice for everyday wellness.</t>
+  </si>
+  <si>
     <t>Herbal Oil</t>
   </si>
   <si>
@@ -1220,6 +1220,9 @@
     <t>ayurvedic herbal hair oil</t>
   </si>
   <si>
+    <t>Every product in our herbal hair oil range is doctor-curated for natural, preventive care, so quality is never left to chance. From everyday nourishment to hair wellness, explore herbal oil, herbal hair growth oil, and ayurvedic herbal hair oil options chosen with care. Time-tested remedies can fit naturally into modern hair care routines.</t>
+  </si>
+  <si>
     <t>Herbal Supplements</t>
   </si>
   <si>
@@ -1403,6 +1406,9 @@
     <t>herbal piles supplements</t>
   </si>
   <si>
+    <t>The herbal piles care range on Cureka is doctor-curated, traditional and genuinely sourced, with authentic products chosen with care. Explore ayurvedic piles care and piles care products, curated around digestive comfort and everyday piles-related discomfort. Time-tested ingredients make natural care a choice you can trust.</t>
+  </si>
+  <si>
     <t>Stress Relief / Sleep</t>
   </si>
   <si>
@@ -1421,6 +1427,9 @@
     <t>herbal sleep support</t>
   </si>
   <si>
+    <t>When stress disrupts your day or sleep, Cureka’s herbal stress relief range brings together time-tested, authentic choices for everyday care. Explore herbal sleep supplements and ayurvedic stress relief options selected around stress, restlessness and disturbed sleep. Rooted in tradition, these gentle choices support a calmer wellness routine.</t>
+  </si>
+  <si>
     <t>Thyroid Care</t>
   </si>
   <si>
@@ -1439,6 +1448,9 @@
     <t>herbal thyroid support</t>
   </si>
   <si>
+    <t>Cureka's approach to herbal thyroid care is simple: doctor-curated with genuine ayurvedic formulations, with authenticity you can always count on. Built around thyroid balance and everyday hormonal wellness, the collection includes ayurvedic thyroid supplements, thyroid support supplements and more to choose from. Age-old remedies, chosen with care, can fit naturally into modern routines.</t>
+  </si>
+  <si>
     <t>Women Health</t>
   </si>
   <si>
@@ -1457,10 +1469,13 @@
     <t>herbal women health products</t>
   </si>
   <si>
+    <t>At Cureka, our herbal women's health range is doctor-curated and rooted in authentic ayurveda, put together for real, everyday needs. Browse through ayurvedic women's health and women health supplements, curated around hormonal balance and everyday women's wellness. There is comfort in choosing care that has stood the test of time.</t>
+  </si>
+  <si>
     <t>Prostate</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/herbal-ayurveda/herbal-supplements/prostate-2</t>
+    <t>https://beta.cureka.com/product-category/herbal-ayurveda/herbal-supplements/prostate</t>
   </si>
   <si>
     <t>herbal prostate care</t>
@@ -1475,6 +1490,9 @@
     <t>herbal prostate supplements</t>
   </si>
   <si>
+    <t>When it comes to herbal prostate care, Cureka's range stays curated with authentic ayurvedic wisdom and never compromises on trust. The range covers concerns such as prostate health and everyday men's wellness, with options like prostate support supplements and ayurvedic prostate care to explore. There is comfort in choosing care that has stood the test of time.</t>
+  </si>
+  <si>
     <t>Herbal kids supplements</t>
   </si>
   <si>
@@ -1844,7 +1862,7 @@
     <t>Vitamins &amp; Supplements</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/nutrition/vitamins-supplements</t>
+    <t>https://beta.cureka.com/product-category/nutrition/supplements</t>
   </si>
   <si>
     <t>vitamins and supplements</t>
@@ -1862,7 +1880,7 @@
     <t>Other Vitamins</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/nutrition/vitamins-supplements/other-vitamins</t>
+    <t>https://beta.cureka.com/product-category/nutrition/supplements/other-vitamins</t>
   </si>
   <si>
     <t>vitamins</t>
@@ -1877,7 +1895,7 @@
     <t>Biotin</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/nutrition/vitamins-supplements/biotin</t>
+    <t>https://beta.cureka.com/product-category/nutrition/supplements/biotin</t>
   </si>
   <si>
     <t>biotin</t>
@@ -1898,7 +1916,7 @@
     <t>Minerals</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/nutrition/vitamins-supplements/minerals</t>
+    <t>https://beta.cureka.com/product-category/nutrition/supplements/minerals</t>
   </si>
   <si>
     <t>mineral supplements</t>
@@ -1913,10 +1931,13 @@
     <t>essential minerals supplements</t>
   </si>
   <si>
+    <t>Cureka keeps its mineral supplement range curated with preventive health in mind, so every pick feels genuine and dependable. Browse through minerals and mineral tablets, curated around nutritional gaps and everyday mineral deficiencies. Long-term wellbeing often starts with the smallest daily choices.</t>
+  </si>
+  <si>
     <t>Speciality Supplements</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/nutrition/vitamins-supplements/speciality-supplements</t>
+    <t>https://beta.cureka.com/product-category/nutrition/supplements/speciality-supplements</t>
   </si>
   <si>
     <t>speciality supplements</t>
@@ -1937,7 +1958,7 @@
     <t>Multivitamins</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/nutrition/vitamins-supplements/multivitamins</t>
+    <t>https://beta.cureka.com/product-category/nutrition/supplements/multivitamins</t>
   </si>
   <si>
     <t>multivitamins</t>
@@ -1958,7 +1979,7 @@
     <t>Amino Acids</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/nutrition/vitamins-supplements/amino-acids</t>
+    <t>https://beta.cureka.com/product-category/nutrition/supplements/amino-acids</t>
   </si>
   <si>
     <t>amino acids</t>
@@ -1979,7 +2000,7 @@
     <t>Calcium</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/nutrition/vitamins-supplements/calcium</t>
+    <t>https://beta.cureka.com/product-category/nutrition/supplements/calcium</t>
   </si>
   <si>
     <t>calcium</t>
@@ -2000,7 +2021,7 @@
     <t>Immunity</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/nutrition/vitamins-supplements/immunity</t>
+    <t>https://beta.cureka.com/product-category/nutrition/supplements/immunity</t>
   </si>
   <si>
     <t>immunity</t>
@@ -2018,7 +2039,7 @@
     <t>Iron</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/nutrition/vitamins-supplements/iron</t>
+    <t>https://beta.cureka.com/product-category/nutrition/supplements/iron</t>
   </si>
   <si>
     <t>iron supplements tablets</t>
@@ -2033,10 +2054,13 @@
     <t>best iron supplements</t>
   </si>
   <si>
+    <t>Cureka's approach to iron supplement is simple: doctor-curated for consistent, everyday nutrition, with authenticity you can always count on. You'll find choices like iron supplement pills and iron supplements here, selected with low haemoglobin, fatigue and everyday iron deficiency in mind. The right nutrition can be a quiet form of everyday self-care.</t>
+  </si>
+  <si>
     <t>Kids Syrup / Drops</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/nutrition/vitamins-supplements/kids-syrup-drops</t>
+    <t>https://beta.cureka.com/product-category/nutrition/supplements/kids-syrup-drops</t>
   </si>
   <si>
     <t>kids vitamins syrup</t>
@@ -2051,10 +2075,13 @@
     <t>vitamin syrup for kids</t>
   </si>
   <si>
+    <t>Cureka's approach to kids vitamin syrup or drops is simple: doctor-curated for everyday preventive health, with authenticity you can always count on. When nutritional gaps and everyday wellness in children matter to you, options like kids vitamin drops and children's supplements make it a little easier. Filling small nutritional gaps today can save bigger worries later.</t>
+  </si>
+  <si>
     <t>Antioxidants</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/nutrition/vitamins-supplements/antioxidants</t>
+    <t>https://beta.cureka.com/product-category/nutrition/supplements/antioxidants</t>
   </si>
   <si>
     <t>antioxidants</t>
@@ -2090,6 +2117,9 @@
     <t>fish oil</t>
   </si>
   <si>
+    <t>When it comes to omega 3 fish oil, Cureka's range stays doctor-approved to support daily wellness and never compromises on trust. Browse through fish oil supplements and omega 3 supplements, curated around heart health, brain function and everyday nutrition. Caring for your health becomes easier when the right essentials are within reach.</t>
+  </si>
+  <si>
     <t>Cod Liver Oil</t>
   </si>
   <si>
@@ -2345,6 +2375,9 @@
     <t>serum and toner</t>
   </si>
   <si>
+    <t>Give your everyday skincare routine a genuine upgrade with Cureka’s face serum range, chosen for trustworthy care and authentic products. Explore skin serum, face toner, and serum and toner options selected for dull, uneven skin and everyday skin concerns. Simple self-care can make a difference in how your skin feels and looks.</t>
+  </si>
+  <si>
     <t>Sunscreen</t>
   </si>
   <si>
@@ -2447,6 +2480,9 @@
     <t>supplements for skin health</t>
   </si>
   <si>
+    <t>At Cureka, our skin supplements range is doctor-curated with ingredients you can trust, put together for real, everyday needs. Discover options including skin health supplements and beauty supplements, put together with skin nutrition, glow and everyday skin health in mind. Self-care is not indulgence, it's a daily act of looking after yourself.</t>
+  </si>
+  <si>
     <t>Lip Care</t>
   </si>
   <si>
@@ -2507,6 +2543,9 @@
     <t>skin care face mask</t>
   </si>
   <si>
+    <t>At Cureka, our face mask range is doctor-curated with ingredients you can trust, put together for real, everyday needs. The range covers concerns such as dull skin, tiredness and the need for a quick skin refresh, with options like facial mask and face masks for skin to explore. The right products can turn a daily habit into a moment of care.</t>
+  </si>
+  <si>
     <t>Scrubs</t>
   </si>
   <si>
@@ -2525,6 +2564,9 @@
     <t>exfoliating scrub</t>
   </si>
   <si>
+    <t>At Cureka, our face scrub range is doctor-curated with ingredients you can trust, put together for real, everyday needs. Explore options such as body scrub and skin scrub, chosen with dead skin build-up and the need for gentle exfoliation in mind. Looking after yourself, in small ways, adds up to feeling more confident.</t>
+  </si>
+  <si>
     <t>Anti Aging</t>
   </si>
   <si>
@@ -2543,6 +2585,9 @@
     <t>anti aging skincare</t>
   </si>
   <si>
+    <t>The anti aging products on Cureka is doctor-curated with ingredients you can trust, with only authentic products making the cut. When dryness, dullness and everyday skin nourishment matter to you, options like anti aging cream and anti aging skin care make it a little easier. The right products can turn a daily habit into a moment of care.</t>
+  </si>
+  <si>
     <t>Body Lotion</t>
   </si>
   <si>
@@ -2666,6 +2711,9 @@
     <t>antifungal skincare products</t>
   </si>
   <si>
+    <t>Our antifungal cream collection stays doctor-curated for authentic, everyday self-care, built around real needs rather than passing trends. Built around dryness, dullness and everyday skin nourishment, the collection includes antifungal skin care, antifungal cream for skin and more to choose from. Feeling good in your own skin often starts with the smallest daily choices.</t>
+  </si>
+  <si>
     <t>Anti Acne</t>
   </si>
   <si>
@@ -2858,7 +2906,7 @@
     <t>Hair Care Supplements</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/personal-care/hair-care/hair-care-supplements-2</t>
+    <t>https://beta.cureka.com/product-category/personal-care/hair-care/hair-care-supplements</t>
   </si>
   <si>
     <t>hair supplements</t>
@@ -3980,7 +4028,7 @@
     <t>Massage Oil</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/sexual-wellness/massage-oil</t>
+    <t>https://beta.cureka.com/product-category/sexual-wellness/massage-oil-sexual-wellness</t>
   </si>
   <si>
     <t>massage oil for men</t>
@@ -3995,6 +4043,9 @@
     <t>men's performance massage oil</t>
   </si>
   <si>
+    <t>At Cureka, massage oil for men products are curated with genuine, judgement-free care in mind, so caring for yourself or your family feels safer. Browse through ayurvedic massage oil for men and massage oil for sexual wellness, curated around intimacy, relaxation and everyday wellness. Comfort and confidence often start with choosing care you can trust.</t>
+  </si>
+  <si>
     <t>Sexual Health Supplements</t>
   </si>
   <si>
@@ -4181,6 +4232,9 @@
     <t>pregnancy test</t>
   </si>
   <si>
+    <t>Every product in our pregnancy test kit range is doctor-curated for genuine care at every stage, so quality is never left to chance. With early pregnancy confirmation and peace of mind in mind, explore choices such as pregnancy detection kit and home pregnancy test in one place. Small comforts can make a real difference on the days that feel hardest.</t>
+  </si>
+  <si>
     <t>Stool Softener</t>
   </si>
   <si>
@@ -4220,10 +4274,13 @@
     <t>postpartum care products</t>
   </si>
   <si>
+    <t>Early motherhood deserves thoughtful care. At Cureka, postpartum care products are doctor-curated to support recovery, comfort, and everyday needs. Explore essentials like post partum care products and postpartum kits, thoughtfully selected to make those early days a little easier.</t>
+  </si>
+  <si>
     <t>Breast pump</t>
   </si>
   <si>
-    <t>https://beta.cureka.com/product-category/women-care/postpartum-care/breast-pump-2</t>
+    <t>https://beta.cureka.com/product-category/women-care/postpartum-care/breast-pump</t>
   </si>
   <si>
     <t>breast pump</t>
@@ -4343,6 +4400,9 @@
     <t>sanitary napkins</t>
   </si>
   <si>
+    <t>Cureka’s sanitary pads selection is doctor-curated for gentle, reliable everyday support — thoughtfully picked, not randomly stocked. Built around period comfort and menstrual hygiene, the collection includes period pads, menstrual pads, sanitary napkins, and more to choose from. The right support can make every period feel a little easier.</t>
+  </si>
+  <si>
     <t>Tampons</t>
   </si>
   <si>
@@ -4425,85 +4485,19 @@
   </si>
   <si>
     <t>Our menopause supplements collection stays chosen to support recovery and everyday comfort, built around real needs rather than passing trends. You'll find choices like menopause support supplements and perimenopause supplements here, selected with hormonal changes and everyday comfort during menopause in mind. Looking after yourself through change is one of the most important things you can do.</t>
-  </si>
-  <si>
-    <t>Cureka keeps its herbal hair oil range doctor-curated for natural, preventive care, making every pick genuine and dependable. The range addresses concerns like hair fall, dandruff, and everyday hair care, with options such as naturals hair shampoo, herbal hair growth oil, and natural shampoo conditioner to explore. Gentle, natural care can be both effective and reassuring.</t>
-  </si>
-  <si>
-    <t>Cureka’s herbal joint care range is doctor-curated for natural, preventive care, with authenticity you can count on. Designed to support concerns like joint stiffness, discomfort, and everyday mobility, the collection includes joint support medicine, natural joint support supplements, and trusted joint care products to explore. Thoughtfully sourced ingredients make natural joint care a dependable choice for everyday wellness.</t>
-  </si>
-  <si>
-    <t>Every product in our herbal hair oil range is doctor-curated for natural, preventive care, so quality is never left to chance. From everyday nourishment to hair wellness, explore herbal oil, herbal hair growth oil, and ayurvedic herbal hair oil options chosen with care. Time-tested remedies can fit naturally into modern hair care routines.</t>
-  </si>
-  <si>
-    <t>The herbal piles care range on Cureka is doctor-curated, traditional and genuinely sourced, with authentic products chosen with care. Explore ayurvedic piles care and piles care products, curated around digestive comfort and everyday piles-related discomfort. Time-tested ingredients make natural care a choice you can trust.</t>
-  </si>
-  <si>
-    <t>When stress disrupts your day or sleep, Cureka’s herbal stress relief range brings together time-tested, authentic choices for everyday care. Explore herbal sleep supplements and ayurvedic stress relief options selected around stress, restlessness and disturbed sleep. Rooted in tradition, these gentle choices support a calmer wellness routine.</t>
-  </si>
-  <si>
-    <t>Cureka's approach to herbal thyroid care is simple: doctor-curated with genuine ayurvedic formulations, with authenticity you can always count on. Built around thyroid balance and everyday hormonal wellness, the collection includes ayurvedic thyroid supplements, thyroid support supplements and more to choose from. Age-old remedies, chosen with care, can fit naturally into modern routines.</t>
-  </si>
-  <si>
-    <t>At Cureka, our herbal women's health range is doctor-curated and rooted in authentic ayurveda, put together for real, everyday needs. Browse through ayurvedic women's health and women health supplements, curated around hormonal balance and everyday women's wellness. There is comfort in choosing care that has stood the test of time.</t>
-  </si>
-  <si>
-    <t>When it comes to herbal prostate care, Cureka's range stays curated with authentic ayurvedic wisdom and never compromises on trust. The range covers concerns such as prostate health and everyday men's wellness, with options like prostate support supplements and ayurvedic prostate care to explore. There is comfort in choosing care that has stood the test of time.</t>
-  </si>
-  <si>
-    <t>Cureka keeps its mineral supplement range curated with preventive health in mind, so every pick feels genuine and dependable. Browse through minerals and mineral tablets, curated around nutritional gaps and everyday mineral deficiencies. Long-term wellbeing often starts with the smallest daily choices.</t>
-  </si>
-  <si>
-    <t>Cureka's approach to iron supplement is simple: doctor-curated for consistent, everyday nutrition, with authenticity you can always count on. You'll find choices like iron supplement pills and iron supplements here, selected with low haemoglobin, fatigue and everyday iron deficiency in mind. The right nutrition can be a quiet form of everyday self-care.</t>
-  </si>
-  <si>
-    <t>Cureka's approach to kids vitamin syrup or drops is simple: doctor-curated for everyday preventive health, with authenticity you can always count on. When nutritional gaps and everyday wellness in children matter to you, options like kids vitamin drops and children's supplements make it a little easier. Filling small nutritional gaps today can save bigger worries later.</t>
-  </si>
-  <si>
-    <t>When it comes to omega 3 fish oil, Cureka's range stays doctor-approved to support daily wellness and never compromises on trust. Browse through fish oil supplements and omega 3 supplements, curated around heart health, brain function and everyday nutrition. Caring for your health becomes easier when the right essentials are within reach.</t>
-  </si>
-  <si>
-    <t>Give your everyday skincare routine a genuine upgrade with Cureka’s face serum range, chosen for trustworthy care and authentic products. Explore skin serum, face toner, and serum and toner options selected for dull, uneven skin and everyday skin concerns. Simple self-care can make a difference in how your skin feels and looks.</t>
-  </si>
-  <si>
-    <t>At Cureka, our skin supplements range is doctor-curated with ingredients you can trust, put together for real, everyday needs. Discover options including skin health supplements and beauty supplements, put together with skin nutrition, glow and everyday skin health in mind. Self-care is not indulgence, it's a daily act of looking after yourself.</t>
-  </si>
-  <si>
-    <t>At Cureka, our face mask range is doctor-curated with ingredients you can trust, put together for real, everyday needs. The range covers concerns such as dull skin, tiredness and the need for a quick skin refresh, with options like facial mask and face masks for skin to explore. The right products can turn a daily habit into a moment of care.</t>
-  </si>
-  <si>
-    <t>At Cureka, our face scrub range is doctor-curated with ingredients you can trust, put together for real, everyday needs. Explore options such as body scrub and skin scrub, chosen with dead skin build-up and the need for gentle exfoliation in mind. Looking after yourself, in small ways, adds up to feeling more confident.</t>
-  </si>
-  <si>
-    <t>The anti aging products on Cureka is doctor-curated with ingredients you can trust, with only authentic products making the cut. When dryness, dullness and everyday skin nourishment matter to you, options like anti aging cream and anti aging skin care make it a little easier. The right products can turn a daily habit into a moment of care.</t>
-  </si>
-  <si>
-    <t>Our antifungal cream collection stays doctor-curated for authentic, everyday self-care, built around real needs rather than passing trends. Built around dryness, dullness and everyday skin nourishment, the collection includes antifungal skin care, antifungal cream for skin and more to choose from. Feeling good in your own skin often starts with the smallest daily choices.</t>
-  </si>
-  <si>
-    <t>At Cureka, massage oil for men products are curated with genuine, judgement-free care in mind, so caring for yourself or your family feels safer. Browse through ayurvedic massage oil for men and massage oil for sexual wellness, curated around intimacy, relaxation and everyday wellness. Comfort and confidence often start with choosing care you can trust.</t>
-  </si>
-  <si>
-    <t>Every product in our pregnancy test kit range is doctor-curated for genuine care at every stage, so quality is never left to chance. With early pregnancy confirmation and peace of mind in mind, explore choices such as pregnancy detection kit and home pregnancy test in one place. Small comforts can make a real difference on the days that feel hardest.</t>
-  </si>
-  <si>
-    <t>Early motherhood deserves thoughtful care. At Cureka, postpartum care products are doctor-curated to support recovery, comfort, and everyday needs. Explore essentials like post partum care products and postpartum kits, thoughtfully selected to make those early days a little easier.</t>
-  </si>
-  <si>
-    <t>Cureka’s sanitary pads selection is doctor-curated for gentle, reliable everyday support — thoughtfully picked, not randomly stocked. Built around period comfort and menstrual hygiene, the collection includes period pads, menstrual pads, sanitary napkins, and more to choose from. The right support can make every period feel a little easier.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -4528,18 +4522,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -4559,10 +4545,13 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4854,13 +4843,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G56"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1" customHeight="1">
+    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4883,7 +4872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="60">
+    <row r="2" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -4906,7 +4895,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="60">
+    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -4929,7 +4918,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60">
+    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -4952,7 +4941,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="60">
+    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -4975,7 +4964,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="60">
+    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -4998,7 +4987,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="60">
+    <row r="7" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -5021,7 +5010,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="60">
+    <row r="8" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -5044,7 +5033,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="60">
+    <row r="9" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -5067,7 +5056,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="60">
+    <row r="10" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>59</v>
       </c>
@@ -5090,7 +5079,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="60">
+    <row r="11" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>63</v>
       </c>
@@ -5113,7 +5102,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="60">
+    <row r="12" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>70</v>
       </c>
@@ -5136,7 +5125,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="60">
+    <row r="13" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -5159,7 +5148,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="60">
+    <row r="14" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -5182,7 +5171,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="60">
+    <row r="15" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>88</v>
       </c>
@@ -5205,7 +5194,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="60">
+    <row r="16" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>95</v>
       </c>
@@ -5228,7 +5217,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="60">
+    <row r="17" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>101</v>
       </c>
@@ -5251,7 +5240,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="60">
+    <row r="18" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>108</v>
       </c>
@@ -5274,7 +5263,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="60">
+    <row r="19" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>114</v>
       </c>
@@ -5297,7 +5286,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="60">
+    <row r="20" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>121</v>
       </c>
@@ -5320,7 +5309,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="60">
+    <row r="21" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>127</v>
       </c>
@@ -5343,7 +5332,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="60">
+    <row r="22" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>134</v>
       </c>
@@ -5366,7 +5355,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="60">
+    <row r="23" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>141</v>
       </c>
@@ -5389,7 +5378,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="60">
+    <row r="24" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>147</v>
       </c>
@@ -5412,7 +5401,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="60">
+    <row r="25" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>154</v>
       </c>
@@ -5435,7 +5424,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="60">
+    <row r="26" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>161</v>
       </c>
@@ -5458,7 +5447,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="60">
+    <row r="27" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>167</v>
       </c>
@@ -5481,7 +5470,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="60">
+    <row r="28" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>173</v>
       </c>
@@ -5504,7 +5493,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="60">
+    <row r="29" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>176</v>
       </c>
@@ -5527,7 +5516,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="60">
+    <row r="30" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>182</v>
       </c>
@@ -5550,7 +5539,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="60">
+    <row r="31" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>185</v>
       </c>
@@ -5573,7 +5562,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="60">
+    <row r="32" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>193</v>
       </c>
@@ -5596,7 +5585,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="60">
+    <row r="33" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>199</v>
       </c>
@@ -5619,7 +5608,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="60">
+    <row r="34" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>205</v>
       </c>
@@ -5642,7 +5631,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="60">
+    <row r="35" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>212</v>
       </c>
@@ -5665,7 +5654,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="60">
+    <row r="36" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>219</v>
       </c>
@@ -5688,7 +5677,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="60">
+    <row r="37" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>225</v>
       </c>
@@ -5711,7 +5700,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="60">
+    <row r="38" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>232</v>
       </c>
@@ -5734,7 +5723,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="60">
+    <row r="39" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>238</v>
       </c>
@@ -5757,7 +5746,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="60">
+    <row r="40" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>245</v>
       </c>
@@ -5780,7 +5769,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="60">
+    <row r="41" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>252</v>
       </c>
@@ -5803,7 +5792,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="60">
+    <row r="42" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>259</v>
       </c>
@@ -5826,7 +5815,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="60">
+    <row r="43" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>266</v>
       </c>
@@ -5849,7 +5838,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="60">
+    <row r="44" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>272</v>
       </c>
@@ -5872,7 +5861,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="60">
+    <row r="45" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>278</v>
       </c>
@@ -5895,7 +5884,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="60">
+    <row r="46" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>284</v>
       </c>
@@ -5918,7 +5907,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="60">
+    <row r="47" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>290</v>
       </c>
@@ -5941,7 +5930,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="60">
+    <row r="48" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>296</v>
       </c>
@@ -5964,7 +5953,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="60">
+    <row r="49" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>302</v>
       </c>
@@ -5987,7 +5976,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="60">
+    <row r="50" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>309</v>
       </c>
@@ -6010,7 +5999,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="60">
+    <row r="51" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>316</v>
       </c>
@@ -6033,7 +6022,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="60">
+    <row r="52" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>322</v>
       </c>
@@ -6056,7 +6045,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="60">
+    <row r="53" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>329</v>
       </c>
@@ -6079,7 +6068,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="60">
+    <row r="54" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>335</v>
       </c>
@@ -6102,7 +6091,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="60">
+    <row r="55" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>341</v>
       </c>
@@ -6125,7 +6114,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="60">
+    <row r="56" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>347</v>
       </c>
@@ -6157,7 +6146,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="23.5703125" customWidth="1"/>
@@ -6166,7 +6155,7 @@
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1" customHeight="1">
+    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>353</v>
       </c>
@@ -6189,7 +6178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="60">
+    <row r="2" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>359</v>
       </c>
@@ -6212,7 +6201,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="60">
+    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>366</v>
       </c>
@@ -6235,7 +6224,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60">
+    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>373</v>
       </c>
@@ -6258,7 +6247,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="60">
+    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>380</v>
       </c>
@@ -6278,388 +6267,388 @@
         <v>385</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1465</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="64.5" customHeight="1">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="6" ht="64.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1466</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="60">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C7" t="s">
         <v>382</v>
       </c>
       <c r="D7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E7" t="s">
         <v>384</v>
       </c>
       <c r="F7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1467</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="60">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B8" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="C8" t="s">
         <v>362</v>
       </c>
       <c r="D8" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E8" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F8" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="60">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B9" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C9" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D9" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E9" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F9" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="60">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B10" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="C10" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D10" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E10" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="F10" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="60">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B11" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C11" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="D11" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E11" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F11" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="60">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B12" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C12" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D12" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E12" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F12" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="60">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B13" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C13" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="D13" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E13" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F13" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="60">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B14" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C14" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D14" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E14" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F14" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="60">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B15" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C15" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D15" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="E15" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F15" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="60">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B16" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C16" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="D16" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E16" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F16" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1468</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="60">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B17" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C17" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D17" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="E17" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F17" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1469</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="60">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B18" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="C18" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="D18" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="E18" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="F18" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1470</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="60">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B19" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C19" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D19" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="E19" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F19" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1471</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="60">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B20" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="C20" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D20" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="E20" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="F20" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1472</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="60">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B21" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="C21" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="D21" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="E21" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="F21" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" copies="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="21.42578125" customWidth="1"/>
@@ -6667,7 +6656,7 @@
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1" customHeight="1">
+    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>353</v>
       </c>
@@ -6690,924 +6679,924 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="60">
+    <row r="2" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="B2" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C2" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="D2" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="E2" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="F2" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="60">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B3" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="C3" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="D3" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="E3" t="s">
+        <v>507</v>
+      </c>
+      <c r="F3" t="s">
+        <v>508</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>510</v>
+      </c>
+      <c r="B4" t="s">
+        <v>511</v>
+      </c>
+      <c r="C4" t="s">
+        <v>506</v>
+      </c>
+      <c r="D4" t="s">
+        <v>512</v>
+      </c>
+      <c r="E4" t="s">
+        <v>513</v>
+      </c>
+      <c r="F4" t="s">
+        <v>514</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>516</v>
+      </c>
+      <c r="B5" t="s">
+        <v>517</v>
+      </c>
+      <c r="C5" t="s">
+        <v>518</v>
+      </c>
+      <c r="D5" t="s">
+        <v>519</v>
+      </c>
+      <c r="E5" t="s">
+        <v>520</v>
+      </c>
+      <c r="F5" t="s">
+        <v>521</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>523</v>
+      </c>
+      <c r="B6" t="s">
+        <v>524</v>
+      </c>
+      <c r="C6" t="s">
+        <v>507</v>
+      </c>
+      <c r="D6" t="s">
+        <v>525</v>
+      </c>
+      <c r="E6" t="s">
+        <v>526</v>
+      </c>
+      <c r="F6" t="s">
+        <v>527</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>529</v>
+      </c>
+      <c r="B7" t="s">
+        <v>530</v>
+      </c>
+      <c r="C7" t="s">
+        <v>508</v>
+      </c>
+      <c r="D7" t="s">
+        <v>531</v>
+      </c>
+      <c r="E7" t="s">
+        <v>532</v>
+      </c>
+      <c r="F7" t="s">
+        <v>533</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>535</v>
+      </c>
+      <c r="B8" t="s">
+        <v>536</v>
+      </c>
+      <c r="C8" t="s">
+        <v>537</v>
+      </c>
+      <c r="D8" t="s">
+        <v>538</v>
+      </c>
+      <c r="E8" t="s">
+        <v>539</v>
+      </c>
+      <c r="F8" t="s">
+        <v>540</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>542</v>
+      </c>
+      <c r="B9" t="s">
+        <v>543</v>
+      </c>
+      <c r="C9" t="s">
+        <v>544</v>
+      </c>
+      <c r="D9" t="s">
+        <v>545</v>
+      </c>
+      <c r="E9" t="s">
+        <v>546</v>
+      </c>
+      <c r="F9" t="s">
+        <v>547</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>549</v>
+      </c>
+      <c r="B10" t="s">
+        <v>550</v>
+      </c>
+      <c r="C10" t="s">
+        <v>551</v>
+      </c>
+      <c r="D10" t="s">
+        <v>552</v>
+      </c>
+      <c r="E10" t="s">
+        <v>553</v>
+      </c>
+      <c r="F10" t="s">
+        <v>554</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>556</v>
+      </c>
+      <c r="B11" t="s">
+        <v>557</v>
+      </c>
+      <c r="C11" t="s">
+        <v>558</v>
+      </c>
+      <c r="D11" t="s">
+        <v>559</v>
+      </c>
+      <c r="E11" t="s">
+        <v>560</v>
+      </c>
+      <c r="F11" t="s">
+        <v>561</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>563</v>
+      </c>
+      <c r="B12" t="s">
+        <v>564</v>
+      </c>
+      <c r="C12" t="s">
+        <v>565</v>
+      </c>
+      <c r="D12" t="s">
+        <v>566</v>
+      </c>
+      <c r="E12" t="s">
+        <v>567</v>
+      </c>
+      <c r="F12" t="s">
+        <v>568</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>570</v>
+      </c>
+      <c r="B13" t="s">
+        <v>571</v>
+      </c>
+      <c r="C13" t="s">
+        <v>572</v>
+      </c>
+      <c r="D13" t="s">
+        <v>573</v>
+      </c>
+      <c r="E13" t="s">
+        <v>574</v>
+      </c>
+      <c r="F13" t="s">
+        <v>575</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>577</v>
+      </c>
+      <c r="B14" t="s">
+        <v>578</v>
+      </c>
+      <c r="C14" t="s">
+        <v>579</v>
+      </c>
+      <c r="D14" t="s">
+        <v>580</v>
+      </c>
+      <c r="E14" t="s">
+        <v>581</v>
+      </c>
+      <c r="F14" t="s">
+        <v>582</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>584</v>
+      </c>
+      <c r="B15" t="s">
+        <v>585</v>
+      </c>
+      <c r="C15" t="s">
+        <v>586</v>
+      </c>
+      <c r="D15" t="s">
+        <v>580</v>
+      </c>
+      <c r="E15" t="s">
+        <v>587</v>
+      </c>
+      <c r="F15" t="s">
+        <v>588</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>590</v>
+      </c>
+      <c r="B16" t="s">
+        <v>591</v>
+      </c>
+      <c r="C16" t="s">
+        <v>592</v>
+      </c>
+      <c r="D16" t="s">
+        <v>593</v>
+      </c>
+      <c r="E16" t="s">
+        <v>594</v>
+      </c>
+      <c r="F16" t="s">
+        <v>595</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>597</v>
+      </c>
+      <c r="B17" t="s">
+        <v>598</v>
+      </c>
+      <c r="C17" t="s">
+        <v>599</v>
+      </c>
+      <c r="D17" t="s">
+        <v>600</v>
+      </c>
+      <c r="E17" t="s">
+        <v>601</v>
+      </c>
+      <c r="F17" t="s">
+        <v>602</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>604</v>
+      </c>
+      <c r="B18" t="s">
+        <v>605</v>
+      </c>
+      <c r="C18" t="s">
+        <v>606</v>
+      </c>
+      <c r="D18" t="s">
+        <v>607</v>
+      </c>
+      <c r="E18" t="s">
+        <v>608</v>
+      </c>
+      <c r="F18" t="s">
+        <v>609</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>611</v>
+      </c>
+      <c r="B19" t="s">
+        <v>612</v>
+      </c>
+      <c r="C19" t="s">
+        <v>613</v>
+      </c>
+      <c r="D19" t="s">
+        <v>614</v>
+      </c>
+      <c r="E19" t="s">
+        <v>615</v>
+      </c>
+      <c r="F19" t="s">
+        <v>501</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>617</v>
+      </c>
+      <c r="B20" t="s">
+        <v>618</v>
+      </c>
+      <c r="C20" t="s">
+        <v>614</v>
+      </c>
+      <c r="D20" t="s">
+        <v>619</v>
+      </c>
+      <c r="E20" t="s">
+        <v>620</v>
+      </c>
+      <c r="F20" t="s">
         <v>499</v>
       </c>
-      <c r="F3" t="s">
-        <v>500</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="60">
-      <c r="A4" t="s">
-        <v>502</v>
-      </c>
-      <c r="B4" t="s">
-        <v>503</v>
-      </c>
-      <c r="C4" t="s">
-        <v>498</v>
-      </c>
-      <c r="D4" t="s">
-        <v>504</v>
-      </c>
-      <c r="E4" t="s">
-        <v>505</v>
-      </c>
-      <c r="F4" t="s">
-        <v>506</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="60">
-      <c r="A5" t="s">
-        <v>508</v>
-      </c>
-      <c r="B5" t="s">
-        <v>509</v>
-      </c>
-      <c r="C5" t="s">
-        <v>510</v>
-      </c>
-      <c r="D5" t="s">
-        <v>511</v>
-      </c>
-      <c r="E5" t="s">
-        <v>512</v>
-      </c>
-      <c r="F5" t="s">
-        <v>513</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="60">
-      <c r="A6" t="s">
-        <v>515</v>
-      </c>
-      <c r="B6" t="s">
-        <v>516</v>
-      </c>
-      <c r="C6" t="s">
-        <v>499</v>
-      </c>
-      <c r="D6" t="s">
-        <v>517</v>
-      </c>
-      <c r="E6" t="s">
-        <v>518</v>
-      </c>
-      <c r="F6" t="s">
-        <v>519</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="60">
-      <c r="A7" t="s">
-        <v>521</v>
-      </c>
-      <c r="B7" t="s">
-        <v>522</v>
-      </c>
-      <c r="C7" t="s">
-        <v>500</v>
-      </c>
-      <c r="D7" t="s">
-        <v>523</v>
-      </c>
-      <c r="E7" t="s">
-        <v>524</v>
-      </c>
-      <c r="F7" t="s">
-        <v>525</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="60">
-      <c r="A8" t="s">
-        <v>527</v>
-      </c>
-      <c r="B8" t="s">
-        <v>528</v>
-      </c>
-      <c r="C8" t="s">
-        <v>529</v>
-      </c>
-      <c r="D8" t="s">
-        <v>530</v>
-      </c>
-      <c r="E8" t="s">
-        <v>531</v>
-      </c>
-      <c r="F8" t="s">
-        <v>532</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="60">
-      <c r="A9" t="s">
-        <v>534</v>
-      </c>
-      <c r="B9" t="s">
-        <v>535</v>
-      </c>
-      <c r="C9" t="s">
-        <v>536</v>
-      </c>
-      <c r="D9" t="s">
-        <v>537</v>
-      </c>
-      <c r="E9" t="s">
-        <v>538</v>
-      </c>
-      <c r="F9" t="s">
-        <v>539</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="60">
-      <c r="A10" t="s">
-        <v>541</v>
-      </c>
-      <c r="B10" t="s">
-        <v>542</v>
-      </c>
-      <c r="C10" t="s">
-        <v>543</v>
-      </c>
-      <c r="D10" t="s">
-        <v>544</v>
-      </c>
-      <c r="E10" t="s">
-        <v>545</v>
-      </c>
-      <c r="F10" t="s">
-        <v>546</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="60">
-      <c r="A11" t="s">
-        <v>548</v>
-      </c>
-      <c r="B11" t="s">
-        <v>549</v>
-      </c>
-      <c r="C11" t="s">
-        <v>550</v>
-      </c>
-      <c r="D11" t="s">
-        <v>551</v>
-      </c>
-      <c r="E11" t="s">
-        <v>552</v>
-      </c>
-      <c r="F11" t="s">
-        <v>553</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="60">
-      <c r="A12" t="s">
-        <v>555</v>
-      </c>
-      <c r="B12" t="s">
-        <v>556</v>
-      </c>
-      <c r="C12" t="s">
-        <v>557</v>
-      </c>
-      <c r="D12" t="s">
-        <v>558</v>
-      </c>
-      <c r="E12" t="s">
-        <v>559</v>
-      </c>
-      <c r="F12" t="s">
-        <v>560</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="60">
-      <c r="A13" t="s">
-        <v>562</v>
-      </c>
-      <c r="B13" t="s">
-        <v>563</v>
-      </c>
-      <c r="C13" t="s">
-        <v>564</v>
-      </c>
-      <c r="D13" t="s">
-        <v>565</v>
-      </c>
-      <c r="E13" t="s">
-        <v>566</v>
-      </c>
-      <c r="F13" t="s">
-        <v>567</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="60">
-      <c r="A14" t="s">
-        <v>569</v>
-      </c>
-      <c r="B14" t="s">
-        <v>570</v>
-      </c>
-      <c r="C14" t="s">
-        <v>571</v>
-      </c>
-      <c r="D14" t="s">
-        <v>572</v>
-      </c>
-      <c r="E14" t="s">
-        <v>573</v>
-      </c>
-      <c r="F14" t="s">
-        <v>574</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="60">
-      <c r="A15" t="s">
-        <v>576</v>
-      </c>
-      <c r="B15" t="s">
-        <v>577</v>
-      </c>
-      <c r="C15" t="s">
-        <v>578</v>
-      </c>
-      <c r="D15" t="s">
-        <v>572</v>
-      </c>
-      <c r="E15" t="s">
-        <v>579</v>
-      </c>
-      <c r="F15" t="s">
-        <v>580</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="45">
-      <c r="A16" t="s">
-        <v>582</v>
-      </c>
-      <c r="B16" t="s">
-        <v>583</v>
-      </c>
-      <c r="C16" t="s">
-        <v>584</v>
-      </c>
-      <c r="D16" t="s">
-        <v>585</v>
-      </c>
-      <c r="E16" t="s">
-        <v>586</v>
-      </c>
-      <c r="F16" t="s">
-        <v>587</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="60">
-      <c r="A17" t="s">
-        <v>589</v>
-      </c>
-      <c r="B17" t="s">
-        <v>590</v>
-      </c>
-      <c r="C17" t="s">
-        <v>591</v>
-      </c>
-      <c r="D17" t="s">
-        <v>592</v>
-      </c>
-      <c r="E17" t="s">
-        <v>593</v>
-      </c>
-      <c r="F17" t="s">
-        <v>594</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="45">
-      <c r="A18" t="s">
-        <v>596</v>
-      </c>
-      <c r="B18" t="s">
-        <v>597</v>
-      </c>
-      <c r="C18" t="s">
-        <v>598</v>
-      </c>
-      <c r="D18" t="s">
-        <v>599</v>
-      </c>
-      <c r="E18" t="s">
-        <v>600</v>
-      </c>
-      <c r="F18" t="s">
-        <v>601</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="60">
-      <c r="A19" t="s">
-        <v>603</v>
-      </c>
-      <c r="B19" t="s">
-        <v>604</v>
-      </c>
-      <c r="C19" t="s">
-        <v>605</v>
-      </c>
-      <c r="D19" t="s">
-        <v>606</v>
-      </c>
-      <c r="E19" t="s">
-        <v>607</v>
-      </c>
-      <c r="F19" t="s">
-        <v>493</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="60">
-      <c r="A20" t="s">
-        <v>609</v>
-      </c>
-      <c r="B20" t="s">
-        <v>610</v>
-      </c>
-      <c r="C20" t="s">
-        <v>606</v>
-      </c>
-      <c r="D20" t="s">
-        <v>611</v>
-      </c>
-      <c r="E20" t="s">
-        <v>612</v>
-      </c>
-      <c r="F20" t="s">
-        <v>491</v>
-      </c>
       <c r="G20" s="2" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="60">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="B21" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
       <c r="C21" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="D21" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="E21" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="F21" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="45">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="B22" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="C22" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="D22" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="E22" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="F22" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1473</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="60">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="B23" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="C23" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="D23" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E23" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="F23" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="60">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="B24" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="C24" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="D24" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="E24" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="F24" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="60">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="B25" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="C25" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="D25" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="E25" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="F25" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="60">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="B26" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="C26" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="D26" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="E26" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="F26" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="60">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="B27" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="C27" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="D27" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E27" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="F27" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="60">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="B28" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="C28" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="D28" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="E28" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="F28" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>1474</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="60">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="B29" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="C29" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="D29" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="E29" t="s">
-        <v>671</v>
+        <v>681</v>
       </c>
       <c r="F29" t="s">
-        <v>672</v>
+        <v>682</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1475</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="60">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="B30" t="s">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="C30" t="s">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="D30" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="E30" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="F30" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="60">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="B31" t="s">
-        <v>681</v>
+        <v>692</v>
       </c>
       <c r="C31" t="s">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="D31" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="E31" t="s">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="F31" t="s">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1476</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="60">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="B32" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="C32" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="D32" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="E32" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="F32" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="60">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>705</v>
+      </c>
+      <c r="B33" t="s">
+        <v>706</v>
+      </c>
+      <c r="C33" t="s">
+        <v>707</v>
+      </c>
+      <c r="D33" t="s">
+        <v>708</v>
+      </c>
+      <c r="E33" t="s">
+        <v>709</v>
+      </c>
+      <c r="F33" t="s">
+        <v>710</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>712</v>
+      </c>
+      <c r="B34" t="s">
+        <v>713</v>
+      </c>
+      <c r="C34" t="s">
+        <v>696</v>
+      </c>
+      <c r="D34" t="s">
+        <v>714</v>
+      </c>
+      <c r="E34" t="s">
+        <v>694</v>
+      </c>
+      <c r="F34" t="s">
         <v>693</v>
       </c>
-      <c r="B33" t="s">
-        <v>694</v>
-      </c>
-      <c r="C33" t="s">
-        <v>695</v>
-      </c>
-      <c r="D33" t="s">
-        <v>696</v>
-      </c>
-      <c r="E33" t="s">
-        <v>697</v>
-      </c>
-      <c r="F33" t="s">
-        <v>698</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="60">
-      <c r="A34" t="s">
-        <v>700</v>
-      </c>
-      <c r="B34" t="s">
-        <v>701</v>
-      </c>
-      <c r="C34" t="s">
-        <v>685</v>
-      </c>
-      <c r="D34" t="s">
-        <v>702</v>
-      </c>
-      <c r="E34" t="s">
-        <v>683</v>
-      </c>
-      <c r="F34" t="s">
-        <v>682</v>
-      </c>
       <c r="G34" s="2" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="60">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="B35" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="C35" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="D35" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="E35" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="F35" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="60">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="B36" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="C36" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="D36" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="E36" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="F36" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="60">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="B37" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="C37" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="D37" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="E37" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="F37" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="60">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="B38" t="s">
+        <v>738</v>
+      </c>
+      <c r="C38" t="s">
         <v>726</v>
       </c>
-      <c r="C38" t="s">
-        <v>714</v>
-      </c>
       <c r="D38" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="E38" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="F38" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="60">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="B39" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="C39" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="D39" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="E39" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="F39" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="60">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="B40" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="C40" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="D40" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="E40" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="F40" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="60">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="B41" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="C41" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="D41" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="E41" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="F41" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
     </row>
   </sheetData>
@@ -7619,7 +7608,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="19.5703125" customWidth="1"/>
@@ -7627,7 +7616,7 @@
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1" customHeight="1">
+    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>353</v>
       </c>
@@ -7650,1223 +7639,1223 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="60">
+    <row r="2" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="B2" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="C2" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="D2" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="E2" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="F2" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="60">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="B3" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="C3" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="D3" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="E3" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="F3" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="60">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="B4" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="C4" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="D4" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="E4" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="F4" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1477</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="60">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>771</v>
+        <v>784</v>
       </c>
       <c r="B5" t="s">
-        <v>772</v>
+        <v>785</v>
       </c>
       <c r="C5" t="s">
-        <v>773</v>
+        <v>786</v>
       </c>
       <c r="D5" t="s">
-        <v>774</v>
+        <v>787</v>
       </c>
       <c r="E5" t="s">
-        <v>775</v>
+        <v>788</v>
       </c>
       <c r="F5" t="s">
-        <v>776</v>
+        <v>789</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="60">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>778</v>
+        <v>791</v>
       </c>
       <c r="B6" t="s">
-        <v>779</v>
+        <v>792</v>
       </c>
       <c r="C6" t="s">
-        <v>780</v>
+        <v>793</v>
       </c>
       <c r="D6" t="s">
-        <v>781</v>
+        <v>794</v>
       </c>
       <c r="E6" t="s">
-        <v>782</v>
+        <v>795</v>
       </c>
       <c r="F6" t="s">
-        <v>783</v>
+        <v>796</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="60">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>785</v>
+        <v>798</v>
       </c>
       <c r="B7" t="s">
-        <v>786</v>
+        <v>799</v>
       </c>
       <c r="C7" t="s">
-        <v>787</v>
+        <v>800</v>
       </c>
       <c r="D7" t="s">
-        <v>788</v>
+        <v>801</v>
       </c>
       <c r="E7" t="s">
-        <v>789</v>
+        <v>802</v>
       </c>
       <c r="F7" t="s">
-        <v>790</v>
+        <v>803</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="45">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>792</v>
+        <v>805</v>
       </c>
       <c r="B8" t="s">
-        <v>793</v>
+        <v>806</v>
       </c>
       <c r="C8" t="s">
-        <v>794</v>
+        <v>807</v>
       </c>
       <c r="D8" t="s">
-        <v>795</v>
+        <v>808</v>
       </c>
       <c r="E8" t="s">
-        <v>796</v>
+        <v>809</v>
       </c>
       <c r="F8" t="s">
-        <v>797</v>
+        <v>810</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="60">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>799</v>
+        <v>812</v>
       </c>
       <c r="B9" t="s">
-        <v>800</v>
+        <v>813</v>
       </c>
       <c r="C9" t="s">
-        <v>801</v>
+        <v>814</v>
       </c>
       <c r="D9" t="s">
-        <v>802</v>
+        <v>815</v>
       </c>
       <c r="E9" t="s">
-        <v>803</v>
+        <v>816</v>
       </c>
       <c r="F9" t="s">
-        <v>804</v>
+        <v>817</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1478</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="45">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>805</v>
+        <v>819</v>
       </c>
       <c r="B10" t="s">
-        <v>806</v>
+        <v>820</v>
       </c>
       <c r="C10" t="s">
-        <v>807</v>
+        <v>821</v>
       </c>
       <c r="D10" t="s">
-        <v>808</v>
+        <v>822</v>
       </c>
       <c r="E10" t="s">
-        <v>809</v>
+        <v>823</v>
       </c>
       <c r="F10" t="s">
-        <v>810</v>
+        <v>824</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="60">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>812</v>
+        <v>826</v>
       </c>
       <c r="B11" t="s">
-        <v>813</v>
+        <v>827</v>
       </c>
       <c r="C11" t="s">
-        <v>814</v>
+        <v>828</v>
       </c>
       <c r="D11" t="s">
-        <v>815</v>
+        <v>829</v>
       </c>
       <c r="E11" t="s">
-        <v>816</v>
+        <v>830</v>
       </c>
       <c r="F11" t="s">
-        <v>817</v>
+        <v>831</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="60">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>819</v>
+        <v>833</v>
       </c>
       <c r="B12" t="s">
-        <v>820</v>
+        <v>834</v>
       </c>
       <c r="C12" t="s">
-        <v>821</v>
+        <v>835</v>
       </c>
       <c r="D12" t="s">
-        <v>822</v>
+        <v>836</v>
       </c>
       <c r="E12" t="s">
-        <v>823</v>
+        <v>837</v>
       </c>
       <c r="F12" t="s">
-        <v>824</v>
+        <v>838</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1479</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="45">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>825</v>
+        <v>840</v>
       </c>
       <c r="B13" t="s">
-        <v>826</v>
+        <v>841</v>
       </c>
       <c r="C13" t="s">
-        <v>827</v>
+        <v>842</v>
       </c>
       <c r="D13" t="s">
-        <v>828</v>
+        <v>843</v>
       </c>
       <c r="E13" t="s">
-        <v>829</v>
+        <v>844</v>
       </c>
       <c r="F13" t="s">
-        <v>830</v>
+        <v>845</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1480</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="60">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>831</v>
+        <v>847</v>
       </c>
       <c r="B14" t="s">
-        <v>832</v>
+        <v>848</v>
       </c>
       <c r="C14" t="s">
-        <v>833</v>
+        <v>849</v>
       </c>
       <c r="D14" t="s">
-        <v>834</v>
+        <v>850</v>
       </c>
       <c r="E14" t="s">
-        <v>835</v>
+        <v>851</v>
       </c>
       <c r="F14" t="s">
-        <v>836</v>
+        <v>852</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1481</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="60">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="B15" t="s">
-        <v>838</v>
+        <v>855</v>
       </c>
       <c r="C15" t="s">
-        <v>839</v>
+        <v>856</v>
       </c>
       <c r="D15" t="s">
-        <v>840</v>
+        <v>857</v>
       </c>
       <c r="E15" t="s">
-        <v>841</v>
+        <v>858</v>
       </c>
       <c r="F15" t="s">
-        <v>842</v>
+        <v>859</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="60">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>844</v>
+        <v>861</v>
       </c>
       <c r="B16" t="s">
-        <v>845</v>
+        <v>862</v>
       </c>
       <c r="C16" t="s">
-        <v>846</v>
+        <v>863</v>
       </c>
       <c r="D16" t="s">
-        <v>847</v>
+        <v>864</v>
       </c>
       <c r="E16" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="F16" t="s">
-        <v>849</v>
+        <v>866</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="60">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>851</v>
+        <v>868</v>
       </c>
       <c r="B17" t="s">
-        <v>852</v>
+        <v>869</v>
       </c>
       <c r="C17" t="s">
-        <v>853</v>
+        <v>870</v>
       </c>
       <c r="D17" t="s">
-        <v>854</v>
+        <v>871</v>
       </c>
       <c r="E17" t="s">
-        <v>855</v>
+        <v>872</v>
       </c>
       <c r="F17" t="s">
-        <v>856</v>
+        <v>873</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="60">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>858</v>
+        <v>875</v>
       </c>
       <c r="B18" t="s">
-        <v>859</v>
+        <v>876</v>
       </c>
       <c r="C18" t="s">
-        <v>860</v>
+        <v>877</v>
       </c>
       <c r="D18" t="s">
-        <v>861</v>
+        <v>878</v>
       </c>
       <c r="E18" t="s">
-        <v>862</v>
+        <v>879</v>
       </c>
       <c r="F18" t="s">
-        <v>863</v>
+        <v>880</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="60">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>865</v>
+        <v>882</v>
       </c>
       <c r="B19" t="s">
-        <v>866</v>
+        <v>883</v>
       </c>
       <c r="C19" t="s">
-        <v>867</v>
+        <v>884</v>
       </c>
       <c r="D19" t="s">
-        <v>868</v>
+        <v>885</v>
       </c>
       <c r="E19" t="s">
-        <v>869</v>
+        <v>886</v>
       </c>
       <c r="F19" t="s">
-        <v>870</v>
+        <v>887</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="60">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>872</v>
+        <v>889</v>
       </c>
       <c r="B20" t="s">
-        <v>873</v>
+        <v>890</v>
       </c>
       <c r="C20" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="D20" t="s">
-        <v>875</v>
+        <v>892</v>
       </c>
       <c r="E20" t="s">
-        <v>876</v>
+        <v>893</v>
       </c>
       <c r="F20" t="s">
-        <v>877</v>
+        <v>894</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1482</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="60">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>878</v>
+        <v>896</v>
       </c>
       <c r="B21" t="s">
-        <v>879</v>
+        <v>897</v>
       </c>
       <c r="C21" t="s">
-        <v>880</v>
+        <v>898</v>
       </c>
       <c r="D21" t="s">
-        <v>881</v>
+        <v>899</v>
       </c>
       <c r="E21" t="s">
-        <v>882</v>
+        <v>900</v>
       </c>
       <c r="F21" t="s">
-        <v>883</v>
+        <v>901</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="60">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="B22" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="C22" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="D22" t="s">
-        <v>888</v>
+        <v>906</v>
       </c>
       <c r="E22" t="s">
-        <v>889</v>
+        <v>907</v>
       </c>
       <c r="F22" t="s">
-        <v>890</v>
+        <v>908</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="60">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>892</v>
+        <v>910</v>
       </c>
       <c r="B23" t="s">
-        <v>893</v>
+        <v>911</v>
       </c>
       <c r="C23" t="s">
-        <v>894</v>
+        <v>912</v>
       </c>
       <c r="D23" t="s">
-        <v>895</v>
+        <v>913</v>
       </c>
       <c r="E23" t="s">
-        <v>896</v>
+        <v>914</v>
       </c>
       <c r="F23" t="s">
-        <v>897</v>
+        <v>915</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="60">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>899</v>
+        <v>917</v>
       </c>
       <c r="B24" t="s">
-        <v>900</v>
+        <v>918</v>
       </c>
       <c r="C24" t="s">
-        <v>901</v>
+        <v>919</v>
       </c>
       <c r="D24" t="s">
-        <v>902</v>
+        <v>920</v>
       </c>
       <c r="E24" t="s">
-        <v>903</v>
+        <v>921</v>
       </c>
       <c r="F24" t="s">
-        <v>904</v>
+        <v>922</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="60">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>906</v>
+        <v>924</v>
       </c>
       <c r="B25" t="s">
-        <v>907</v>
+        <v>925</v>
       </c>
       <c r="C25" t="s">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="D25" t="s">
-        <v>909</v>
+        <v>927</v>
       </c>
       <c r="E25" t="s">
-        <v>910</v>
+        <v>928</v>
       </c>
       <c r="F25" t="s">
-        <v>911</v>
+        <v>929</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="60">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>913</v>
+        <v>931</v>
       </c>
       <c r="B26" t="s">
-        <v>914</v>
+        <v>932</v>
       </c>
       <c r="C26" t="s">
-        <v>915</v>
+        <v>933</v>
       </c>
       <c r="D26" t="s">
-        <v>916</v>
+        <v>934</v>
       </c>
       <c r="E26" t="s">
-        <v>917</v>
+        <v>935</v>
       </c>
       <c r="F26" t="s">
-        <v>918</v>
+        <v>936</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="60">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>920</v>
+        <v>938</v>
       </c>
       <c r="B27" t="s">
-        <v>921</v>
+        <v>939</v>
       </c>
       <c r="C27" t="s">
-        <v>922</v>
+        <v>940</v>
       </c>
       <c r="D27" t="s">
-        <v>923</v>
+        <v>941</v>
       </c>
       <c r="E27" t="s">
-        <v>924</v>
+        <v>942</v>
       </c>
       <c r="F27" t="s">
-        <v>925</v>
+        <v>943</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="60">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>927</v>
+        <v>945</v>
       </c>
       <c r="B28" t="s">
-        <v>928</v>
+        <v>946</v>
       </c>
       <c r="C28" t="s">
-        <v>929</v>
+        <v>947</v>
       </c>
       <c r="D28" t="s">
-        <v>930</v>
+        <v>948</v>
       </c>
       <c r="E28" t="s">
-        <v>931</v>
+        <v>949</v>
       </c>
       <c r="F28" t="s">
-        <v>932</v>
+        <v>950</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="47.25" customHeight="1">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="29" ht="47.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>934</v>
+        <v>952</v>
       </c>
       <c r="B29" t="s">
-        <v>935</v>
+        <v>953</v>
       </c>
       <c r="C29" t="s">
-        <v>936</v>
+        <v>954</v>
       </c>
       <c r="D29" t="s">
-        <v>937</v>
+        <v>955</v>
       </c>
       <c r="E29" t="s">
-        <v>938</v>
+        <v>956</v>
       </c>
       <c r="F29" t="s">
-        <v>939</v>
+        <v>957</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="60">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>941</v>
+        <v>959</v>
       </c>
       <c r="B30" t="s">
-        <v>942</v>
+        <v>960</v>
       </c>
       <c r="C30" t="s">
-        <v>943</v>
+        <v>961</v>
       </c>
       <c r="D30" t="s">
-        <v>944</v>
+        <v>962</v>
       </c>
       <c r="E30" t="s">
-        <v>945</v>
+        <v>963</v>
       </c>
       <c r="F30" t="s">
-        <v>946</v>
+        <v>964</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="60">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>948</v>
+        <v>966</v>
       </c>
       <c r="B31" t="s">
-        <v>949</v>
+        <v>967</v>
       </c>
       <c r="C31" t="s">
-        <v>950</v>
+        <v>968</v>
       </c>
       <c r="D31" t="s">
-        <v>951</v>
+        <v>969</v>
       </c>
       <c r="E31" t="s">
-        <v>952</v>
+        <v>970</v>
       </c>
       <c r="F31" t="s">
-        <v>953</v>
+        <v>971</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="60">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>955</v>
+        <v>973</v>
       </c>
       <c r="B32" t="s">
-        <v>956</v>
+        <v>974</v>
       </c>
       <c r="C32" t="s">
-        <v>957</v>
+        <v>975</v>
       </c>
       <c r="D32" t="s">
-        <v>958</v>
+        <v>976</v>
       </c>
       <c r="E32" t="s">
-        <v>959</v>
+        <v>977</v>
       </c>
       <c r="F32" t="s">
-        <v>960</v>
+        <v>978</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="60">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>962</v>
+        <v>980</v>
       </c>
       <c r="B33" t="s">
-        <v>963</v>
+        <v>981</v>
       </c>
       <c r="C33" t="s">
-        <v>964</v>
+        <v>982</v>
       </c>
       <c r="D33" t="s">
-        <v>965</v>
+        <v>983</v>
       </c>
       <c r="E33" t="s">
-        <v>966</v>
+        <v>984</v>
       </c>
       <c r="F33" t="s">
-        <v>967</v>
+        <v>985</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="60">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>969</v>
+        <v>987</v>
       </c>
       <c r="B34" t="s">
-        <v>970</v>
+        <v>988</v>
       </c>
       <c r="C34" t="s">
-        <v>971</v>
+        <v>989</v>
       </c>
       <c r="D34" t="s">
-        <v>972</v>
+        <v>990</v>
       </c>
       <c r="E34" t="s">
-        <v>973</v>
+        <v>991</v>
       </c>
       <c r="F34" t="s">
-        <v>974</v>
+        <v>992</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="45">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>976</v>
+        <v>994</v>
       </c>
       <c r="B35" t="s">
-        <v>977</v>
+        <v>995</v>
       </c>
       <c r="C35" t="s">
-        <v>978</v>
+        <v>996</v>
       </c>
       <c r="D35" t="s">
-        <v>979</v>
+        <v>997</v>
       </c>
       <c r="E35" t="s">
-        <v>980</v>
+        <v>998</v>
       </c>
       <c r="F35" t="s">
-        <v>981</v>
+        <v>999</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="60">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>983</v>
+        <v>1001</v>
       </c>
       <c r="B36" t="s">
-        <v>984</v>
+        <v>1002</v>
       </c>
       <c r="C36" t="s">
-        <v>985</v>
+        <v>1003</v>
       </c>
       <c r="D36" t="s">
-        <v>986</v>
+        <v>1004</v>
       </c>
       <c r="E36" t="s">
-        <v>987</v>
+        <v>1005</v>
       </c>
       <c r="F36" t="s">
-        <v>988</v>
+        <v>1006</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="62.25" customHeight="1">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="37" ht="62.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>990</v>
+        <v>1008</v>
       </c>
       <c r="B37" t="s">
-        <v>991</v>
+        <v>1009</v>
       </c>
       <c r="C37" t="s">
-        <v>992</v>
+        <v>1010</v>
       </c>
       <c r="D37" t="s">
-        <v>993</v>
+        <v>1011</v>
       </c>
       <c r="E37" t="s">
-        <v>994</v>
+        <v>1012</v>
       </c>
       <c r="F37" t="s">
-        <v>995</v>
+        <v>1013</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="47.25" customHeight="1">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="38" ht="47.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>997</v>
+        <v>1015</v>
       </c>
       <c r="B38" t="s">
-        <v>998</v>
+        <v>1016</v>
       </c>
       <c r="C38" t="s">
-        <v>999</v>
+        <v>1017</v>
       </c>
       <c r="D38" t="s">
-        <v>1000</v>
+        <v>1018</v>
       </c>
       <c r="E38" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="F38" t="s">
-        <v>1002</v>
+        <v>1020</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="50.25" customHeight="1">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="39" ht="50.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1004</v>
+        <v>1022</v>
       </c>
       <c r="B39" t="s">
-        <v>1005</v>
+        <v>1023</v>
       </c>
       <c r="C39" t="s">
-        <v>1006</v>
+        <v>1024</v>
       </c>
       <c r="D39" t="s">
-        <v>1007</v>
+        <v>1025</v>
       </c>
       <c r="E39" t="s">
-        <v>1008</v>
+        <v>1026</v>
       </c>
       <c r="F39" t="s">
-        <v>1009</v>
+        <v>1027</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="60">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>1011</v>
+        <v>1029</v>
       </c>
       <c r="B40" t="s">
-        <v>1012</v>
+        <v>1030</v>
       </c>
       <c r="C40" t="s">
-        <v>1013</v>
+        <v>1031</v>
       </c>
       <c r="D40" t="s">
-        <v>1014</v>
+        <v>1032</v>
       </c>
       <c r="E40" t="s">
-        <v>1015</v>
+        <v>1033</v>
       </c>
       <c r="F40" t="s">
-        <v>1016</v>
+        <v>1034</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="60">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1018</v>
+        <v>1036</v>
       </c>
       <c r="B41" t="s">
-        <v>1019</v>
+        <v>1037</v>
       </c>
       <c r="C41" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="D41" t="s">
-        <v>1020</v>
+        <v>1038</v>
       </c>
       <c r="E41" t="s">
-        <v>607</v>
+        <v>615</v>
       </c>
       <c r="F41" t="s">
-        <v>1021</v>
+        <v>1039</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="60">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1023</v>
+        <v>1041</v>
       </c>
       <c r="B42" t="s">
-        <v>1024</v>
+        <v>1042</v>
       </c>
       <c r="C42" t="s">
-        <v>1025</v>
+        <v>1043</v>
       </c>
       <c r="D42" t="s">
-        <v>1026</v>
+        <v>1044</v>
       </c>
       <c r="E42" t="s">
-        <v>1027</v>
+        <v>1045</v>
       </c>
       <c r="F42" t="s">
-        <v>1028</v>
+        <v>1046</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>1029</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="60">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>1030</v>
+        <v>1048</v>
       </c>
       <c r="B43" t="s">
-        <v>1031</v>
+        <v>1049</v>
       </c>
       <c r="C43" t="s">
-        <v>1032</v>
+        <v>1050</v>
       </c>
       <c r="D43" t="s">
-        <v>1033</v>
+        <v>1051</v>
       </c>
       <c r="E43" t="s">
-        <v>1034</v>
+        <v>1052</v>
       </c>
       <c r="F43" t="s">
-        <v>1035</v>
+        <v>1053</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="45">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="44" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>1037</v>
+        <v>1055</v>
       </c>
       <c r="B44" t="s">
-        <v>1038</v>
+        <v>1056</v>
       </c>
       <c r="C44" t="s">
-        <v>1039</v>
+        <v>1057</v>
       </c>
       <c r="D44" t="s">
-        <v>1040</v>
+        <v>1058</v>
       </c>
       <c r="E44" t="s">
-        <v>1041</v>
+        <v>1059</v>
       </c>
       <c r="F44" t="s">
-        <v>1042</v>
+        <v>1060</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="60">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1044</v>
+        <v>1062</v>
       </c>
       <c r="B45" t="s">
-        <v>1045</v>
+        <v>1063</v>
       </c>
       <c r="C45" t="s">
-        <v>1046</v>
+        <v>1064</v>
       </c>
       <c r="D45" t="s">
-        <v>1047</v>
+        <v>1065</v>
       </c>
       <c r="E45" t="s">
-        <v>1048</v>
+        <v>1066</v>
       </c>
       <c r="F45" t="s">
-        <v>1049</v>
+        <v>1067</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="60">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>1051</v>
+        <v>1069</v>
       </c>
       <c r="B46" t="s">
-        <v>1052</v>
+        <v>1070</v>
       </c>
       <c r="C46" t="s">
-        <v>1053</v>
+        <v>1071</v>
       </c>
       <c r="D46" t="s">
-        <v>1054</v>
+        <v>1072</v>
       </c>
       <c r="E46" t="s">
-        <v>1055</v>
+        <v>1073</v>
       </c>
       <c r="F46" t="s">
-        <v>1056</v>
+        <v>1074</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="60">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>1058</v>
+        <v>1076</v>
       </c>
       <c r="B47" t="s">
-        <v>1059</v>
+        <v>1077</v>
       </c>
       <c r="C47" t="s">
-        <v>1060</v>
+        <v>1078</v>
       </c>
       <c r="D47" t="s">
-        <v>1061</v>
+        <v>1079</v>
       </c>
       <c r="E47" t="s">
-        <v>1062</v>
+        <v>1080</v>
       </c>
       <c r="F47" t="s">
-        <v>1063</v>
+        <v>1081</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="60">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1065</v>
+        <v>1083</v>
       </c>
       <c r="B48" t="s">
-        <v>1066</v>
+        <v>1084</v>
       </c>
       <c r="C48" t="s">
-        <v>1067</v>
+        <v>1085</v>
       </c>
       <c r="D48" t="s">
-        <v>1068</v>
+        <v>1086</v>
       </c>
       <c r="E48" t="s">
-        <v>1069</v>
+        <v>1087</v>
       </c>
       <c r="F48" t="s">
-        <v>1070</v>
+        <v>1088</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="60">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>1072</v>
+        <v>1090</v>
       </c>
       <c r="B49" t="s">
-        <v>1073</v>
+        <v>1091</v>
       </c>
       <c r="C49" t="s">
-        <v>1074</v>
+        <v>1092</v>
       </c>
       <c r="D49" t="s">
-        <v>1075</v>
+        <v>1093</v>
       </c>
       <c r="E49" t="s">
-        <v>1076</v>
+        <v>1094</v>
       </c>
       <c r="F49" t="s">
-        <v>1077</v>
+        <v>1095</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="45">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="50" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1079</v>
+        <v>1097</v>
       </c>
       <c r="B50" t="s">
-        <v>1080</v>
+        <v>1098</v>
       </c>
       <c r="C50" t="s">
-        <v>1081</v>
+        <v>1099</v>
       </c>
       <c r="D50" t="s">
-        <v>1082</v>
+        <v>1100</v>
       </c>
       <c r="E50" t="s">
-        <v>1083</v>
+        <v>1101</v>
       </c>
       <c r="F50" t="s">
-        <v>1084</v>
+        <v>1102</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="60">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>1086</v>
+        <v>1104</v>
       </c>
       <c r="B51" t="s">
-        <v>1087</v>
+        <v>1105</v>
       </c>
       <c r="C51" t="s">
-        <v>1088</v>
+        <v>1106</v>
       </c>
       <c r="D51" t="s">
-        <v>1089</v>
+        <v>1107</v>
       </c>
       <c r="E51" t="s">
-        <v>1090</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="s">
-        <v>1091</v>
+        <v>1109</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="60">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>1093</v>
+        <v>1111</v>
       </c>
       <c r="B52" t="s">
-        <v>1094</v>
+        <v>1112</v>
       </c>
       <c r="C52" t="s">
-        <v>1095</v>
+        <v>1113</v>
       </c>
       <c r="D52" t="s">
-        <v>1096</v>
+        <v>1114</v>
       </c>
       <c r="E52" t="s">
-        <v>1097</v>
+        <v>1115</v>
       </c>
       <c r="F52" t="s">
-        <v>1098</v>
+        <v>1116</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="60">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>1100</v>
+        <v>1118</v>
       </c>
       <c r="B53" t="s">
-        <v>1101</v>
+        <v>1119</v>
       </c>
       <c r="C53" t="s">
-        <v>1102</v>
+        <v>1120</v>
       </c>
       <c r="D53" t="s">
-        <v>1103</v>
+        <v>1121</v>
       </c>
       <c r="E53" t="s">
-        <v>1104</v>
+        <v>1122</v>
       </c>
       <c r="F53" t="s">
-        <v>1105</v>
+        <v>1123</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="60">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1107</v>
+        <v>1125</v>
       </c>
       <c r="B54" t="s">
-        <v>1108</v>
+        <v>1126</v>
       </c>
       <c r="C54" t="s">
-        <v>1109</v>
+        <v>1127</v>
       </c>
       <c r="D54" t="s">
-        <v>1110</v>
+        <v>1128</v>
       </c>
       <c r="E54" t="s">
-        <v>1111</v>
+        <v>1129</v>
       </c>
       <c r="F54" t="s">
-        <v>1112</v>
+        <v>1130</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>1113</v>
+        <v>1131</v>
       </c>
     </row>
   </sheetData>
@@ -8878,7 +8867,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
@@ -8886,7 +8875,7 @@
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1" customHeight="1">
+    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>353</v>
       </c>
@@ -8909,602 +8898,602 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="60">
+    <row r="2" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1114</v>
+        <v>1132</v>
       </c>
       <c r="B2" t="s">
-        <v>1115</v>
+        <v>1133</v>
       </c>
       <c r="C2" t="s">
-        <v>1116</v>
+        <v>1134</v>
       </c>
       <c r="D2" t="s">
-        <v>1117</v>
+        <v>1135</v>
       </c>
       <c r="E2" t="s">
-        <v>1118</v>
+        <v>1136</v>
       </c>
       <c r="F2" t="s">
-        <v>1119</v>
+        <v>1137</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="60">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1121</v>
+        <v>1139</v>
       </c>
       <c r="B3" t="s">
-        <v>1122</v>
+        <v>1140</v>
       </c>
       <c r="C3" t="s">
-        <v>1123</v>
+        <v>1141</v>
       </c>
       <c r="D3" t="s">
-        <v>1124</v>
+        <v>1142</v>
       </c>
       <c r="E3" t="s">
-        <v>1125</v>
+        <v>1143</v>
       </c>
       <c r="F3" t="s">
-        <v>1126</v>
+        <v>1144</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="60">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1128</v>
+        <v>1146</v>
       </c>
       <c r="B4" t="s">
-        <v>1129</v>
+        <v>1147</v>
       </c>
       <c r="C4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1185</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1196</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1204</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F12" t="s">
         <v>1130</v>
       </c>
-      <c r="D4" t="s">
-        <v>1131</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1132</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1133</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>1134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="60">
-      <c r="A5" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1137</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1138</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1139</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="60">
-      <c r="A6" t="s">
-        <v>1141</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1143</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1144</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1145</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1146</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="60">
-      <c r="A7" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1149</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1150</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1151</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1152</v>
-      </c>
-      <c r="F7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>1154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="60">
-      <c r="A8" t="s">
-        <v>1155</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1158</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1159</v>
-      </c>
-      <c r="F8" t="s">
-        <v>1160</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="60">
-      <c r="A9" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1164</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1165</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1166</v>
-      </c>
-      <c r="F9" t="s">
-        <v>1167</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>1168</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="60">
-      <c r="A10" t="s">
-        <v>1169</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1171</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1172</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1173</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1174</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="60">
-      <c r="A11" t="s">
-        <v>1176</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1177</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1178</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1179</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1180</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1181</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="60">
-      <c r="A12" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1185</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1186</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1187</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1112</v>
-      </c>
       <c r="G12" s="2" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="60">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1189</v>
+        <v>1207</v>
       </c>
       <c r="B13" t="s">
-        <v>1190</v>
+        <v>1208</v>
       </c>
       <c r="C13" t="s">
-        <v>1191</v>
+        <v>1209</v>
       </c>
       <c r="D13" t="s">
-        <v>1192</v>
+        <v>1210</v>
       </c>
       <c r="E13" t="s">
-        <v>1193</v>
+        <v>1211</v>
       </c>
       <c r="F13" t="s">
-        <v>1194</v>
+        <v>1212</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="60">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1196</v>
+        <v>1214</v>
       </c>
       <c r="B14" t="s">
-        <v>1197</v>
+        <v>1215</v>
       </c>
       <c r="C14" t="s">
-        <v>1198</v>
+        <v>1216</v>
       </c>
       <c r="D14" t="s">
-        <v>1199</v>
+        <v>1217</v>
       </c>
       <c r="E14" t="s">
-        <v>1200</v>
+        <v>1218</v>
       </c>
       <c r="F14" t="s">
-        <v>1201</v>
+        <v>1219</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="60">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1203</v>
+        <v>1221</v>
       </c>
       <c r="B15" t="s">
-        <v>1204</v>
+        <v>1222</v>
       </c>
       <c r="C15" t="s">
-        <v>1205</v>
+        <v>1223</v>
       </c>
       <c r="D15" t="s">
-        <v>1206</v>
+        <v>1224</v>
       </c>
       <c r="E15" t="s">
-        <v>1207</v>
+        <v>1225</v>
       </c>
       <c r="F15" t="s">
-        <v>1208</v>
+        <v>1226</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="60">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>1210</v>
+        <v>1228</v>
       </c>
       <c r="B16" t="s">
-        <v>1211</v>
+        <v>1229</v>
       </c>
       <c r="C16" t="s">
-        <v>1212</v>
+        <v>1230</v>
       </c>
       <c r="D16" t="s">
-        <v>1213</v>
+        <v>1231</v>
       </c>
       <c r="E16" t="s">
-        <v>1214</v>
+        <v>1232</v>
       </c>
       <c r="F16" t="s">
-        <v>1215</v>
+        <v>1233</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="60">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>1217</v>
+        <v>1235</v>
       </c>
       <c r="B17" t="s">
-        <v>1218</v>
+        <v>1236</v>
       </c>
       <c r="C17" t="s">
-        <v>1219</v>
+        <v>1237</v>
       </c>
       <c r="D17" t="s">
-        <v>1220</v>
+        <v>1238</v>
       </c>
       <c r="E17" t="s">
-        <v>1221</v>
+        <v>1239</v>
       </c>
       <c r="F17" t="s">
-        <v>1222</v>
+        <v>1240</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1223</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="60">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>1224</v>
+        <v>1242</v>
       </c>
       <c r="B18" t="s">
-        <v>1225</v>
+        <v>1243</v>
       </c>
       <c r="C18" t="s">
-        <v>1226</v>
+        <v>1244</v>
       </c>
       <c r="D18" t="s">
-        <v>1227</v>
+        <v>1245</v>
       </c>
       <c r="E18" t="s">
-        <v>1228</v>
+        <v>1246</v>
       </c>
       <c r="F18" t="s">
-        <v>1229</v>
+        <v>1247</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="45">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1231</v>
+        <v>1249</v>
       </c>
       <c r="B19" t="s">
-        <v>1232</v>
+        <v>1250</v>
       </c>
       <c r="C19" t="s">
-        <v>1233</v>
+        <v>1251</v>
       </c>
       <c r="D19" t="s">
-        <v>1234</v>
+        <v>1252</v>
       </c>
       <c r="E19" t="s">
-        <v>1235</v>
+        <v>1253</v>
       </c>
       <c r="F19" t="s">
-        <v>1236</v>
+        <v>1254</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="60">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1238</v>
+        <v>1256</v>
       </c>
       <c r="B20" t="s">
-        <v>1239</v>
+        <v>1257</v>
       </c>
       <c r="C20" t="s">
-        <v>1240</v>
+        <v>1258</v>
       </c>
       <c r="D20" t="s">
-        <v>1241</v>
+        <v>1259</v>
       </c>
       <c r="E20" t="s">
-        <v>1242</v>
+        <v>1260</v>
       </c>
       <c r="F20" t="s">
-        <v>1243</v>
+        <v>1261</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="60">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1245</v>
+        <v>1263</v>
       </c>
       <c r="B21" t="s">
-        <v>1246</v>
+        <v>1264</v>
       </c>
       <c r="C21" t="s">
-        <v>1247</v>
+        <v>1265</v>
       </c>
       <c r="D21" t="s">
-        <v>1248</v>
+        <v>1266</v>
       </c>
       <c r="E21" t="s">
-        <v>1249</v>
+        <v>1267</v>
       </c>
       <c r="F21" t="s">
-        <v>1250</v>
+        <v>1268</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="60">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1252</v>
+        <v>1270</v>
       </c>
       <c r="B22" t="s">
-        <v>1253</v>
+        <v>1271</v>
       </c>
       <c r="C22" t="s">
-        <v>1254</v>
+        <v>1272</v>
       </c>
       <c r="D22" t="s">
-        <v>1255</v>
+        <v>1273</v>
       </c>
       <c r="E22" t="s">
-        <v>1256</v>
+        <v>1274</v>
       </c>
       <c r="F22" t="s">
-        <v>1257</v>
+        <v>1275</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="60">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1259</v>
+        <v>1277</v>
       </c>
       <c r="B23" t="s">
-        <v>1260</v>
+        <v>1278</v>
       </c>
       <c r="C23" t="s">
-        <v>1261</v>
+        <v>1279</v>
       </c>
       <c r="D23" t="s">
-        <v>1262</v>
+        <v>1280</v>
       </c>
       <c r="E23" t="s">
-        <v>1263</v>
+        <v>1281</v>
       </c>
       <c r="F23" t="s">
-        <v>1264</v>
+        <v>1282</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="60">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1266</v>
+        <v>1284</v>
       </c>
       <c r="B24" t="s">
-        <v>1267</v>
+        <v>1285</v>
       </c>
       <c r="C24" t="s">
-        <v>1268</v>
+        <v>1286</v>
       </c>
       <c r="D24" t="s">
-        <v>1269</v>
+        <v>1287</v>
       </c>
       <c r="E24" t="s">
-        <v>1270</v>
+        <v>1288</v>
       </c>
       <c r="F24" t="s">
-        <v>1271</v>
+        <v>1289</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="60">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1273</v>
+        <v>1291</v>
       </c>
       <c r="B25" t="s">
-        <v>1274</v>
+        <v>1292</v>
       </c>
       <c r="C25" t="s">
-        <v>1275</v>
+        <v>1293</v>
       </c>
       <c r="D25" t="s">
-        <v>1276</v>
+        <v>1294</v>
       </c>
       <c r="E25" t="s">
-        <v>1277</v>
+        <v>1295</v>
       </c>
       <c r="F25" t="s">
-        <v>1278</v>
+        <v>1296</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="60">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1280</v>
+        <v>1298</v>
       </c>
       <c r="B26" t="s">
-        <v>1281</v>
+        <v>1299</v>
       </c>
       <c r="C26" t="s">
-        <v>1282</v>
+        <v>1300</v>
       </c>
       <c r="D26" t="s">
-        <v>1283</v>
+        <v>1301</v>
       </c>
       <c r="E26" t="s">
-        <v>1284</v>
+        <v>1302</v>
       </c>
       <c r="F26" t="s">
-        <v>1285</v>
+        <v>1303</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="60">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1287</v>
+        <v>1305</v>
       </c>
       <c r="B27" t="s">
-        <v>1288</v>
+        <v>1306</v>
       </c>
       <c r="C27" t="s">
-        <v>1289</v>
+        <v>1307</v>
       </c>
       <c r="D27" t="s">
-        <v>1290</v>
+        <v>1308</v>
       </c>
       <c r="E27" t="s">
-        <v>1291</v>
+        <v>1309</v>
       </c>
       <c r="F27" t="s">
-        <v>1292</v>
+        <v>1310</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>1293</v>
+        <v>1311</v>
       </c>
     </row>
   </sheetData>
@@ -9516,7 +9505,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="21.42578125" customWidth="1"/>
@@ -9524,7 +9513,7 @@
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1" customHeight="1">
+    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>353</v>
       </c>
@@ -9547,119 +9536,119 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45">
+    <row r="2" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1294</v>
+        <v>1312</v>
       </c>
       <c r="B2" t="s">
-        <v>1295</v>
+        <v>1313</v>
       </c>
       <c r="C2" t="s">
-        <v>1296</v>
+        <v>1314</v>
       </c>
       <c r="D2" t="s">
-        <v>1297</v>
+        <v>1315</v>
       </c>
       <c r="E2" t="s">
-        <v>1298</v>
+        <v>1316</v>
       </c>
       <c r="F2" t="s">
-        <v>1299</v>
+        <v>1317</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="60">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1301</v>
+        <v>1319</v>
       </c>
       <c r="B3" t="s">
-        <v>1302</v>
+        <v>1320</v>
       </c>
       <c r="C3" t="s">
-        <v>1303</v>
+        <v>1321</v>
       </c>
       <c r="D3" t="s">
-        <v>1304</v>
+        <v>1322</v>
       </c>
       <c r="E3" t="s">
-        <v>1305</v>
+        <v>1323</v>
       </c>
       <c r="F3" t="s">
-        <v>1306</v>
+        <v>1324</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="60">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1308</v>
+        <v>1326</v>
       </c>
       <c r="B4" t="s">
-        <v>1309</v>
+        <v>1327</v>
       </c>
       <c r="C4" t="s">
-        <v>1310</v>
+        <v>1328</v>
       </c>
       <c r="D4" t="s">
-        <v>1311</v>
+        <v>1329</v>
       </c>
       <c r="E4" t="s">
-        <v>1312</v>
+        <v>1330</v>
       </c>
       <c r="F4" t="s">
-        <v>1313</v>
+        <v>1331</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="60">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1315</v>
+        <v>1333</v>
       </c>
       <c r="B5" t="s">
-        <v>1316</v>
+        <v>1334</v>
       </c>
       <c r="C5" t="s">
-        <v>1317</v>
+        <v>1335</v>
       </c>
       <c r="D5" t="s">
-        <v>1318</v>
+        <v>1336</v>
       </c>
       <c r="E5" t="s">
-        <v>1319</v>
+        <v>1337</v>
       </c>
       <c r="F5" t="s">
-        <v>1320</v>
+        <v>1338</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1483</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="60">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1321</v>
+        <v>1340</v>
       </c>
       <c r="B6" t="s">
-        <v>1322</v>
+        <v>1341</v>
       </c>
       <c r="C6" t="s">
-        <v>1323</v>
+        <v>1342</v>
       </c>
       <c r="D6" t="s">
-        <v>1324</v>
+        <v>1343</v>
       </c>
       <c r="E6" t="s">
-        <v>1325</v>
+        <v>1344</v>
       </c>
       <c r="F6" t="s">
-        <v>1326</v>
+        <v>1345</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1327</v>
+        <v>1346</v>
       </c>
     </row>
   </sheetData>
@@ -9671,7 +9660,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
@@ -9679,7 +9668,7 @@
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32.1" customHeight="1">
+    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>353</v>
       </c>
@@ -9702,464 +9691,464 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="60">
+    <row r="2" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1328</v>
+        <v>1347</v>
       </c>
       <c r="B2" t="s">
-        <v>1329</v>
+        <v>1348</v>
       </c>
       <c r="C2" t="s">
-        <v>1330</v>
+        <v>1349</v>
       </c>
       <c r="D2" t="s">
-        <v>1331</v>
+        <v>1350</v>
       </c>
       <c r="E2" t="s">
-        <v>1332</v>
+        <v>1351</v>
       </c>
       <c r="F2" t="s">
-        <v>1333</v>
+        <v>1352</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="60">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1335</v>
+        <v>1354</v>
       </c>
       <c r="B3" t="s">
-        <v>1336</v>
+        <v>1355</v>
       </c>
       <c r="C3" t="s">
-        <v>1337</v>
+        <v>1356</v>
       </c>
       <c r="D3" t="s">
-        <v>1338</v>
+        <v>1357</v>
       </c>
       <c r="E3" t="s">
-        <v>1339</v>
+        <v>1358</v>
       </c>
       <c r="F3" t="s">
-        <v>1340</v>
+        <v>1359</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="60">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1342</v>
+        <v>1361</v>
       </c>
       <c r="B4" t="s">
-        <v>1343</v>
+        <v>1362</v>
       </c>
       <c r="C4" t="s">
-        <v>1344</v>
+        <v>1363</v>
       </c>
       <c r="D4" t="s">
-        <v>1345</v>
+        <v>1364</v>
       </c>
       <c r="E4" t="s">
-        <v>1346</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="s">
-        <v>1347</v>
+        <v>1366</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="60">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1349</v>
+        <v>1368</v>
       </c>
       <c r="B5" t="s">
-        <v>1350</v>
+        <v>1369</v>
       </c>
       <c r="C5" t="s">
-        <v>1351</v>
+        <v>1370</v>
       </c>
       <c r="D5" t="s">
-        <v>1352</v>
+        <v>1371</v>
       </c>
       <c r="E5" t="s">
-        <v>1353</v>
+        <v>1372</v>
       </c>
       <c r="F5" t="s">
-        <v>1354</v>
+        <v>1373</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>1355</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="60">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1356</v>
+        <v>1375</v>
       </c>
       <c r="B6" t="s">
-        <v>1357</v>
+        <v>1376</v>
       </c>
       <c r="C6" t="s">
-        <v>1358</v>
+        <v>1377</v>
       </c>
       <c r="D6" t="s">
-        <v>1359</v>
+        <v>1378</v>
       </c>
       <c r="E6" t="s">
-        <v>1360</v>
+        <v>1379</v>
       </c>
       <c r="F6" t="s">
-        <v>1361</v>
+        <v>1380</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="60">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1363</v>
+        <v>1382</v>
       </c>
       <c r="B7" t="s">
-        <v>1364</v>
+        <v>1383</v>
       </c>
       <c r="C7" t="s">
-        <v>1365</v>
+        <v>1384</v>
       </c>
       <c r="D7" t="s">
-        <v>1366</v>
+        <v>1385</v>
       </c>
       <c r="E7" t="s">
-        <v>1367</v>
+        <v>1386</v>
       </c>
       <c r="F7" t="s">
-        <v>1368</v>
+        <v>1387</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="60">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1370</v>
+        <v>1389</v>
       </c>
       <c r="B8" t="s">
-        <v>1371</v>
+        <v>1390</v>
       </c>
       <c r="C8" t="s">
-        <v>1372</v>
+        <v>1391</v>
       </c>
       <c r="D8" t="s">
-        <v>1373</v>
+        <v>1392</v>
       </c>
       <c r="E8" t="s">
-        <v>1374</v>
+        <v>1393</v>
       </c>
       <c r="F8" t="s">
-        <v>1375</v>
+        <v>1394</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="60">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1377</v>
+        <v>1396</v>
       </c>
       <c r="B9" t="s">
-        <v>1378</v>
+        <v>1397</v>
       </c>
       <c r="C9" t="s">
-        <v>1379</v>
+        <v>1398</v>
       </c>
       <c r="D9" t="s">
-        <v>1380</v>
+        <v>1399</v>
       </c>
       <c r="E9" t="s">
-        <v>1381</v>
+        <v>1400</v>
       </c>
       <c r="F9" t="s">
-        <v>1382</v>
+        <v>1401</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1408</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="11" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1411</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1414</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1415</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1418</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1420</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1421</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>1423</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1434</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1435</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1436</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>1444</v>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1448</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1453</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1457</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>1458</v>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1464</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1471</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E21" t="s">
         <v>1484</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="60">
-      <c r="A10" t="s">
-        <v>1383</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1384</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1385</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1386</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1387</v>
-      </c>
-      <c r="F10" t="s">
-        <v>1388</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>1389</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="45">
-      <c r="A11" t="s">
-        <v>1390</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1391</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1392</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1393</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1394</v>
-      </c>
-      <c r="F11" t="s">
-        <v>1395</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="F21" t="s">
         <v>1485</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="60">
-      <c r="A12" t="s">
-        <v>1396</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1397</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1398</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1399</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1400</v>
-      </c>
-      <c r="F12" t="s">
-        <v>1401</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>1402</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="60">
-      <c r="A13" t="s">
-        <v>1403</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1404</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1405</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1406</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1407</v>
-      </c>
-      <c r="F13" t="s">
-        <v>1408</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>1409</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="60">
-      <c r="A14" t="s">
-        <v>1410</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1411</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1412</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1413</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1414</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1415</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>1416</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="60">
-      <c r="A15" t="s">
-        <v>1417</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1418</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1419</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1420</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1421</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1422</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>1423</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="60">
-      <c r="A16" t="s">
-        <v>1424</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1425</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1426</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1427</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1428</v>
-      </c>
-      <c r="F16" t="s">
-        <v>1429</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="60">
-      <c r="A17" t="s">
-        <v>1431</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1432</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1433</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1434</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1435</v>
-      </c>
-      <c r="F17" t="s">
-        <v>1436</v>
-      </c>
-      <c r="G17" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>1486</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="60">
-      <c r="A18" t="s">
-        <v>1437</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1438</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1439</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1440</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1441</v>
-      </c>
-      <c r="F18" t="s">
-        <v>1442</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>1443</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="60">
-      <c r="A19" t="s">
-        <v>1444</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1445</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1446</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1447</v>
-      </c>
-      <c r="E19" t="s">
-        <v>1448</v>
-      </c>
-      <c r="F19" t="s">
-        <v>1449</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="60">
-      <c r="A20" t="s">
-        <v>1451</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1452</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1453</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1454</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1455</v>
-      </c>
-      <c r="F20" t="s">
-        <v>1456</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>1457</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="60">
-      <c r="A21" t="s">
-        <v>1458</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1459</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1460</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1461</v>
-      </c>
-      <c r="E21" t="s">
-        <v>1462</v>
-      </c>
-      <c r="F21" t="s">
-        <v>1463</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>1464</v>
       </c>
     </row>
   </sheetData>
@@ -10170,8 +10159,8 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Master-Data-Sheets/cureka_category_page_descriptions_above the fold.xlsx
+++ b/docs/Master-Data-Sheets/cureka_category_page_descriptions_above the fold.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="1" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11760" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="healthcare devices" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Herbal &amp; Ayurvedha" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="vitamins &amp; nutrition" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="personal care" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="baby care" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="sexual wellness" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="women care" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Sheet1" state="visible" r:id="rId11"/>
+    <sheet name="healthcare devices" sheetId="1" r:id="rId1"/>
+    <sheet name="Herbal &amp; Ayurvedha" sheetId="2" r:id="rId2"/>
+    <sheet name="vitamins &amp; nutrition" sheetId="3" r:id="rId3"/>
+    <sheet name="personal care" sheetId="4" r:id="rId4"/>
+    <sheet name="baby care" sheetId="5" r:id="rId5"/>
+    <sheet name="sexual wellness" sheetId="6" r:id="rId6"/>
+    <sheet name="women care" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">'women care'!$A$1:$G$21</definedName>
@@ -4490,14 +4490,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -4522,10 +4522,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -4843,13 +4851,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G56"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="32.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4872,7 +4880,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="60" customHeight="1">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -4895,7 +4903,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="60" customHeight="1">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -4918,7 +4926,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="60" customHeight="1">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -4941,7 +4949,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="60" customHeight="1">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -4964,7 +4972,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="60" customHeight="1">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -4987,7 +4995,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="60" customHeight="1">
       <c r="A7" t="s">
         <v>41</v>
       </c>
@@ -5010,7 +5018,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="60" customHeight="1">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -5033,7 +5041,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="60" customHeight="1">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -5056,7 +5064,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="60" customHeight="1">
       <c r="A10" t="s">
         <v>59</v>
       </c>
@@ -5079,7 +5087,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="60" customHeight="1">
       <c r="A11" t="s">
         <v>63</v>
       </c>
@@ -5102,7 +5110,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="60" customHeight="1">
       <c r="A12" t="s">
         <v>70</v>
       </c>
@@ -5125,7 +5133,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="60" customHeight="1">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -5148,7 +5156,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="60" customHeight="1">
       <c r="A14" t="s">
         <v>82</v>
       </c>
@@ -5171,7 +5179,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="60" customHeight="1">
       <c r="A15" t="s">
         <v>88</v>
       </c>
@@ -5194,7 +5202,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="60" customHeight="1">
       <c r="A16" t="s">
         <v>95</v>
       </c>
@@ -5217,7 +5225,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="60" customHeight="1">
       <c r="A17" t="s">
         <v>101</v>
       </c>
@@ -5240,7 +5248,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="60" customHeight="1">
       <c r="A18" t="s">
         <v>108</v>
       </c>
@@ -5263,7 +5271,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="60" customHeight="1">
       <c r="A19" t="s">
         <v>114</v>
       </c>
@@ -5286,7 +5294,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="60" customHeight="1">
       <c r="A20" t="s">
         <v>121</v>
       </c>
@@ -5309,7 +5317,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="60" customHeight="1">
       <c r="A21" t="s">
         <v>127</v>
       </c>
@@ -5332,7 +5340,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="60" customHeight="1">
       <c r="A22" t="s">
         <v>134</v>
       </c>
@@ -5355,7 +5363,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="60" customHeight="1">
       <c r="A23" t="s">
         <v>141</v>
       </c>
@@ -5378,7 +5386,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="60" customHeight="1">
       <c r="A24" t="s">
         <v>147</v>
       </c>
@@ -5401,7 +5409,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="60" customHeight="1">
       <c r="A25" t="s">
         <v>154</v>
       </c>
@@ -5424,7 +5432,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="60" customHeight="1">
       <c r="A26" t="s">
         <v>161</v>
       </c>
@@ -5447,7 +5455,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="60" customHeight="1">
       <c r="A27" t="s">
         <v>167</v>
       </c>
@@ -5470,7 +5478,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="60" customHeight="1">
       <c r="A28" t="s">
         <v>173</v>
       </c>
@@ -5493,7 +5501,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="60" customHeight="1">
       <c r="A29" t="s">
         <v>176</v>
       </c>
@@ -5516,7 +5524,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="60" customHeight="1">
       <c r="A30" t="s">
         <v>182</v>
       </c>
@@ -5539,7 +5547,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="60" customHeight="1">
       <c r="A31" t="s">
         <v>185</v>
       </c>
@@ -5562,7 +5570,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="60" customHeight="1">
       <c r="A32" t="s">
         <v>193</v>
       </c>
@@ -5585,7 +5593,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="60" customHeight="1">
       <c r="A33" t="s">
         <v>199</v>
       </c>
@@ -5608,7 +5616,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="60" customHeight="1">
       <c r="A34" t="s">
         <v>205</v>
       </c>
@@ -5631,7 +5639,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="60" customHeight="1">
       <c r="A35" t="s">
         <v>212</v>
       </c>
@@ -5654,7 +5662,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="60" customHeight="1">
       <c r="A36" t="s">
         <v>219</v>
       </c>
@@ -5677,7 +5685,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="60" customHeight="1">
       <c r="A37" t="s">
         <v>225</v>
       </c>
@@ -5700,7 +5708,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="60" customHeight="1">
       <c r="A38" t="s">
         <v>232</v>
       </c>
@@ -5723,7 +5731,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="60" customHeight="1">
       <c r="A39" t="s">
         <v>238</v>
       </c>
@@ -5746,7 +5754,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="60" customHeight="1">
       <c r="A40" t="s">
         <v>245</v>
       </c>
@@ -5769,7 +5777,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="60" customHeight="1">
       <c r="A41" t="s">
         <v>252</v>
       </c>
@@ -5792,7 +5800,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="60" customHeight="1">
       <c r="A42" t="s">
         <v>259</v>
       </c>
@@ -5815,7 +5823,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="60" customHeight="1">
       <c r="A43" t="s">
         <v>266</v>
       </c>
@@ -5838,7 +5846,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="60" customHeight="1">
       <c r="A44" t="s">
         <v>272</v>
       </c>
@@ -5861,7 +5869,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="60" customHeight="1">
       <c r="A45" t="s">
         <v>278</v>
       </c>
@@ -5884,7 +5892,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="60" customHeight="1">
       <c r="A46" t="s">
         <v>284</v>
       </c>
@@ -5907,7 +5915,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="60" customHeight="1">
       <c r="A47" t="s">
         <v>290</v>
       </c>
@@ -5930,7 +5938,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="60" customHeight="1">
       <c r="A48" t="s">
         <v>296</v>
       </c>
@@ -5953,7 +5961,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="60" customHeight="1">
       <c r="A49" t="s">
         <v>302</v>
       </c>
@@ -5976,7 +5984,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="50" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="60" customHeight="1">
       <c r="A50" t="s">
         <v>309</v>
       </c>
@@ -5999,7 +6007,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="60" customHeight="1">
       <c r="A51" t="s">
         <v>316</v>
       </c>
@@ -6022,7 +6030,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="60" customHeight="1">
       <c r="A52" t="s">
         <v>322</v>
       </c>
@@ -6045,7 +6053,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="60" customHeight="1">
       <c r="A53" t="s">
         <v>329</v>
       </c>
@@ -6068,7 +6076,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="60" customHeight="1">
       <c r="A54" t="s">
         <v>335</v>
       </c>
@@ -6091,7 +6099,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="55" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="60" customHeight="1">
       <c r="A55" t="s">
         <v>341</v>
       </c>
@@ -6114,7 +6122,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="56" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="60" customHeight="1">
       <c r="A56" t="s">
         <v>347</v>
       </c>
@@ -6146,16 +6154,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" customWidth="1"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="76" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" customWidth="1"/>
+    <col min="4" max="4" width="23.109375" customWidth="1"/>
     <col min="5" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="32.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>353</v>
       </c>
@@ -6178,7 +6187,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="60" customHeight="1">
       <c r="A2" t="s">
         <v>359</v>
       </c>
@@ -6201,7 +6210,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="60" customHeight="1">
       <c r="A3" t="s">
         <v>366</v>
       </c>
@@ -6224,7 +6233,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="60" customHeight="1">
       <c r="A4" t="s">
         <v>373</v>
       </c>
@@ -6247,7 +6256,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="60" customHeight="1">
       <c r="A5" t="s">
         <v>380</v>
       </c>
@@ -6270,7 +6279,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="6" ht="64.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="64.5" customHeight="1">
       <c r="A6" t="s">
         <v>387</v>
       </c>
@@ -6293,7 +6302,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="60" customHeight="1">
       <c r="A7" t="s">
         <v>394</v>
       </c>
@@ -6316,7 +6325,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="60" customHeight="1">
       <c r="A8" t="s">
         <v>399</v>
       </c>
@@ -6339,7 +6348,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="60" customHeight="1">
       <c r="A9" t="s">
         <v>405</v>
       </c>
@@ -6362,7 +6371,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="60" customHeight="1">
       <c r="A10" t="s">
         <v>412</v>
       </c>
@@ -6385,7 +6394,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="60" customHeight="1">
       <c r="A11" t="s">
         <v>419</v>
       </c>
@@ -6408,7 +6417,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="60" customHeight="1">
       <c r="A12" t="s">
         <v>426</v>
       </c>
@@ -6431,7 +6440,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="60" customHeight="1">
       <c r="A13" t="s">
         <v>433</v>
       </c>
@@ -6454,7 +6463,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="60" customHeight="1">
       <c r="A14" t="s">
         <v>440</v>
       </c>
@@ -6477,7 +6486,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="60" customHeight="1">
       <c r="A15" t="s">
         <v>447</v>
       </c>
@@ -6500,7 +6509,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="60" customHeight="1">
       <c r="A16" t="s">
         <v>454</v>
       </c>
@@ -6523,7 +6532,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="60" customHeight="1">
       <c r="A17" t="s">
         <v>461</v>
       </c>
@@ -6546,7 +6555,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="60" customHeight="1">
       <c r="A18" t="s">
         <v>468</v>
       </c>
@@ -6569,7 +6578,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="60" customHeight="1">
       <c r="A19" t="s">
         <v>475</v>
       </c>
@@ -6592,7 +6601,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="60" customHeight="1">
       <c r="A20" t="s">
         <v>482</v>
       </c>
@@ -6615,7 +6624,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="60" customHeight="1">
       <c r="A21" t="s">
         <v>489</v>
       </c>
@@ -6641,22 +6650,22 @@
   </sheetData>
   <autoFilter ref="A1:G21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="0"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="0" copies="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" customWidth="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="32.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>353</v>
       </c>
@@ -6679,7 +6688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="60" customHeight="1">
       <c r="A2" t="s">
         <v>496</v>
       </c>
@@ -6702,7 +6711,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="60" customHeight="1">
       <c r="A3" t="s">
         <v>503</v>
       </c>
@@ -6725,7 +6734,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="60" customHeight="1">
       <c r="A4" t="s">
         <v>510</v>
       </c>
@@ -6748,7 +6757,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="60" customHeight="1">
       <c r="A5" t="s">
         <v>516</v>
       </c>
@@ -6771,7 +6780,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="60" customHeight="1">
       <c r="A6" t="s">
         <v>523</v>
       </c>
@@ -6794,7 +6803,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="60" customHeight="1">
       <c r="A7" t="s">
         <v>529</v>
       </c>
@@ -6817,7 +6826,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="60" customHeight="1">
       <c r="A8" t="s">
         <v>535</v>
       </c>
@@ -6840,7 +6849,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="60" customHeight="1">
       <c r="A9" t="s">
         <v>542</v>
       </c>
@@ -6863,7 +6872,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="60" customHeight="1">
       <c r="A10" t="s">
         <v>549</v>
       </c>
@@ -6886,7 +6895,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="60" customHeight="1">
       <c r="A11" t="s">
         <v>556</v>
       </c>
@@ -6909,7 +6918,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="60" customHeight="1">
       <c r="A12" t="s">
         <v>563</v>
       </c>
@@ -6932,7 +6941,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="60" customHeight="1">
       <c r="A13" t="s">
         <v>570</v>
       </c>
@@ -6955,7 +6964,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="60" customHeight="1">
       <c r="A14" t="s">
         <v>577</v>
       </c>
@@ -6978,7 +6987,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="60" customHeight="1">
       <c r="A15" t="s">
         <v>584</v>
       </c>
@@ -7001,7 +7010,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="16" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="45" customHeight="1">
       <c r="A16" t="s">
         <v>590</v>
       </c>
@@ -7024,7 +7033,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="60" customHeight="1">
       <c r="A17" t="s">
         <v>597</v>
       </c>
@@ -7047,7 +7056,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="18" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="45" customHeight="1">
       <c r="A18" t="s">
         <v>604</v>
       </c>
@@ -7070,7 +7079,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="60" customHeight="1">
       <c r="A19" t="s">
         <v>611</v>
       </c>
@@ -7093,7 +7102,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="60" customHeight="1">
       <c r="A20" t="s">
         <v>617</v>
       </c>
@@ -7116,7 +7125,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="60" customHeight="1">
       <c r="A21" t="s">
         <v>622</v>
       </c>
@@ -7139,7 +7148,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="22" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="45" customHeight="1">
       <c r="A22" t="s">
         <v>629</v>
       </c>
@@ -7162,7 +7171,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="60" customHeight="1">
       <c r="A23" t="s">
         <v>636</v>
       </c>
@@ -7185,7 +7194,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="60" customHeight="1">
       <c r="A24" t="s">
         <v>643</v>
       </c>
@@ -7208,7 +7217,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="60" customHeight="1">
       <c r="A25" t="s">
         <v>650</v>
       </c>
@@ -7231,7 +7240,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="60" customHeight="1">
       <c r="A26" t="s">
         <v>657</v>
       </c>
@@ -7254,7 +7263,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="60" customHeight="1">
       <c r="A27" t="s">
         <v>664</v>
       </c>
@@ -7277,7 +7286,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="60" customHeight="1">
       <c r="A28" t="s">
         <v>670</v>
       </c>
@@ -7300,7 +7309,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="60" customHeight="1">
       <c r="A29" t="s">
         <v>677</v>
       </c>
@@ -7323,7 +7332,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="60" customHeight="1">
       <c r="A30" t="s">
         <v>684</v>
       </c>
@@ -7346,7 +7355,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="60" customHeight="1">
       <c r="A31" t="s">
         <v>691</v>
       </c>
@@ -7369,7 +7378,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="60" customHeight="1">
       <c r="A32" t="s">
         <v>698</v>
       </c>
@@ -7392,7 +7401,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="60" customHeight="1">
       <c r="A33" t="s">
         <v>705</v>
       </c>
@@ -7415,7 +7424,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="60" customHeight="1">
       <c r="A34" t="s">
         <v>712</v>
       </c>
@@ -7438,7 +7447,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="35" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="60" customHeight="1">
       <c r="A35" t="s">
         <v>716</v>
       </c>
@@ -7461,7 +7470,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="60" customHeight="1">
       <c r="A36" t="s">
         <v>723</v>
       </c>
@@ -7484,7 +7493,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="37" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="60" customHeight="1">
       <c r="A37" t="s">
         <v>730</v>
       </c>
@@ -7507,7 +7516,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="38" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="60" customHeight="1">
       <c r="A38" t="s">
         <v>737</v>
       </c>
@@ -7530,7 +7539,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="39" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="60" customHeight="1">
       <c r="A39" t="s">
         <v>743</v>
       </c>
@@ -7553,7 +7562,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="60" customHeight="1">
       <c r="A40" t="s">
         <v>750</v>
       </c>
@@ -7576,7 +7585,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="60" customHeight="1">
       <c r="A41" t="s">
         <v>757</v>
       </c>
@@ -7608,15 +7617,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.5546875" customWidth="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="32.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>353</v>
       </c>
@@ -7639,7 +7648,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="60" customHeight="1">
       <c r="A2" t="s">
         <v>763</v>
       </c>
@@ -7662,7 +7671,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="60" customHeight="1">
       <c r="A3" t="s">
         <v>770</v>
       </c>
@@ -7685,7 +7694,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="60" customHeight="1">
       <c r="A4" t="s">
         <v>777</v>
       </c>
@@ -7708,7 +7717,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="60" customHeight="1">
       <c r="A5" t="s">
         <v>784</v>
       </c>
@@ -7731,7 +7740,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="60" customHeight="1">
       <c r="A6" t="s">
         <v>791</v>
       </c>
@@ -7754,7 +7763,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="60" customHeight="1">
       <c r="A7" t="s">
         <v>798</v>
       </c>
@@ -7777,7 +7786,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="45" customHeight="1">
       <c r="A8" t="s">
         <v>805</v>
       </c>
@@ -7800,7 +7809,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="60" customHeight="1">
       <c r="A9" t="s">
         <v>812</v>
       </c>
@@ -7823,7 +7832,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="45" customHeight="1">
       <c r="A10" t="s">
         <v>819</v>
       </c>
@@ -7846,7 +7855,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="60" customHeight="1">
       <c r="A11" t="s">
         <v>826</v>
       </c>
@@ -7869,7 +7878,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="60" customHeight="1">
       <c r="A12" t="s">
         <v>833</v>
       </c>
@@ -7892,7 +7901,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="13" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="45" customHeight="1">
       <c r="A13" t="s">
         <v>840</v>
       </c>
@@ -7915,7 +7924,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="60" customHeight="1">
       <c r="A14" t="s">
         <v>847</v>
       </c>
@@ -7938,7 +7947,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="60" customHeight="1">
       <c r="A15" t="s">
         <v>854</v>
       </c>
@@ -7961,7 +7970,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="60" customHeight="1">
       <c r="A16" t="s">
         <v>861</v>
       </c>
@@ -7984,7 +7993,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="60" customHeight="1">
       <c r="A17" t="s">
         <v>868</v>
       </c>
@@ -8007,7 +8016,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="60" customHeight="1">
       <c r="A18" t="s">
         <v>875</v>
       </c>
@@ -8030,7 +8039,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="60" customHeight="1">
       <c r="A19" t="s">
         <v>882</v>
       </c>
@@ -8053,7 +8062,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="60" customHeight="1">
       <c r="A20" t="s">
         <v>889</v>
       </c>
@@ -8076,7 +8085,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="60" customHeight="1">
       <c r="A21" t="s">
         <v>896</v>
       </c>
@@ -8099,7 +8108,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="60" customHeight="1">
       <c r="A22" t="s">
         <v>903</v>
       </c>
@@ -8122,7 +8131,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="60" customHeight="1">
       <c r="A23" t="s">
         <v>910</v>
       </c>
@@ -8145,7 +8154,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="60" customHeight="1">
       <c r="A24" t="s">
         <v>917</v>
       </c>
@@ -8168,7 +8177,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="60" customHeight="1">
       <c r="A25" t="s">
         <v>924</v>
       </c>
@@ -8191,7 +8200,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="60" customHeight="1">
       <c r="A26" t="s">
         <v>931</v>
       </c>
@@ -8214,7 +8223,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="60" customHeight="1">
       <c r="A27" t="s">
         <v>938</v>
       </c>
@@ -8237,7 +8246,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="60" customHeight="1">
       <c r="A28" t="s">
         <v>945</v>
       </c>
@@ -8260,7 +8269,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="29" ht="47.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="47.25" customHeight="1">
       <c r="A29" t="s">
         <v>952</v>
       </c>
@@ -8283,7 +8292,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="60" customHeight="1">
       <c r="A30" t="s">
         <v>959</v>
       </c>
@@ -8306,7 +8315,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="31" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="60" customHeight="1">
       <c r="A31" t="s">
         <v>966</v>
       </c>
@@ -8329,7 +8338,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="32" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="60" customHeight="1">
       <c r="A32" t="s">
         <v>973</v>
       </c>
@@ -8352,7 +8361,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="33" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="60" customHeight="1">
       <c r="A33" t="s">
         <v>980</v>
       </c>
@@ -8375,7 +8384,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="60" customHeight="1">
       <c r="A34" t="s">
         <v>987</v>
       </c>
@@ -8398,7 +8407,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="35" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="45" customHeight="1">
       <c r="A35" t="s">
         <v>994</v>
       </c>
@@ -8421,7 +8430,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="60" customHeight="1">
       <c r="A36" t="s">
         <v>1001</v>
       </c>
@@ -8444,7 +8453,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="37" ht="62.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="62.25" customHeight="1">
       <c r="A37" t="s">
         <v>1008</v>
       </c>
@@ -8467,7 +8476,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="38" ht="47.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="47.25" customHeight="1">
       <c r="A38" t="s">
         <v>1015</v>
       </c>
@@ -8490,7 +8499,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="39" ht="50.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="50.25" customHeight="1">
       <c r="A39" t="s">
         <v>1022</v>
       </c>
@@ -8513,7 +8522,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="40" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="60" customHeight="1">
       <c r="A40" t="s">
         <v>1029</v>
       </c>
@@ -8536,7 +8545,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="41" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="60" customHeight="1">
       <c r="A41" t="s">
         <v>1036</v>
       </c>
@@ -8559,7 +8568,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="42" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="60" customHeight="1">
       <c r="A42" t="s">
         <v>1041</v>
       </c>
@@ -8582,7 +8591,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="43" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="60" customHeight="1">
       <c r="A43" t="s">
         <v>1048</v>
       </c>
@@ -8605,7 +8614,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="44" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="45" customHeight="1">
       <c r="A44" t="s">
         <v>1055</v>
       </c>
@@ -8628,7 +8637,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="45" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="60" customHeight="1">
       <c r="A45" t="s">
         <v>1062</v>
       </c>
@@ -8651,7 +8660,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="46" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="60" customHeight="1">
       <c r="A46" t="s">
         <v>1069</v>
       </c>
@@ -8674,7 +8683,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="60" customHeight="1">
       <c r="A47" t="s">
         <v>1076</v>
       </c>
@@ -8697,7 +8706,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="48" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="60" customHeight="1">
       <c r="A48" t="s">
         <v>1083</v>
       </c>
@@ -8720,7 +8729,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="49" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="60" customHeight="1">
       <c r="A49" t="s">
         <v>1090</v>
       </c>
@@ -8743,7 +8752,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="50" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="45" customHeight="1">
       <c r="A50" t="s">
         <v>1097</v>
       </c>
@@ -8766,7 +8775,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="51" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="60" customHeight="1">
       <c r="A51" t="s">
         <v>1104</v>
       </c>
@@ -8789,7 +8798,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="52" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="60" customHeight="1">
       <c r="A52" t="s">
         <v>1111</v>
       </c>
@@ -8812,7 +8821,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="60" customHeight="1">
       <c r="A53" t="s">
         <v>1118</v>
       </c>
@@ -8835,7 +8844,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="54" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="60" customHeight="1">
       <c r="A54" t="s">
         <v>1125</v>
       </c>
@@ -8867,15 +8876,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="32.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>353</v>
       </c>
@@ -8898,7 +8907,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="60" customHeight="1">
       <c r="A2" t="s">
         <v>1132</v>
       </c>
@@ -8921,7 +8930,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="60" customHeight="1">
       <c r="A3" t="s">
         <v>1139</v>
       </c>
@@ -8944,7 +8953,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="60" customHeight="1">
       <c r="A4" t="s">
         <v>1146</v>
       </c>
@@ -8967,7 +8976,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="60" customHeight="1">
       <c r="A5" t="s">
         <v>1153</v>
       </c>
@@ -8990,7 +8999,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="60" customHeight="1">
       <c r="A6" t="s">
         <v>1159</v>
       </c>
@@ -9013,7 +9022,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="60" customHeight="1">
       <c r="A7" t="s">
         <v>1166</v>
       </c>
@@ -9036,7 +9045,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="60" customHeight="1">
       <c r="A8" t="s">
         <v>1173</v>
       </c>
@@ -9059,7 +9068,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="60" customHeight="1">
       <c r="A9" t="s">
         <v>1180</v>
       </c>
@@ -9082,7 +9091,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="60" customHeight="1">
       <c r="A10" t="s">
         <v>1187</v>
       </c>
@@ -9105,7 +9114,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="60" customHeight="1">
       <c r="A11" t="s">
         <v>1194</v>
       </c>
@@ -9128,7 +9137,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="60" customHeight="1">
       <c r="A12" t="s">
         <v>1201</v>
       </c>
@@ -9151,7 +9160,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="60" customHeight="1">
       <c r="A13" t="s">
         <v>1207</v>
       </c>
@@ -9174,7 +9183,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="60" customHeight="1">
       <c r="A14" t="s">
         <v>1214</v>
       </c>
@@ -9197,7 +9206,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="60" customHeight="1">
       <c r="A15" t="s">
         <v>1221</v>
       </c>
@@ -9220,7 +9229,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="60" customHeight="1">
       <c r="A16" t="s">
         <v>1228</v>
       </c>
@@ -9243,7 +9252,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="60" customHeight="1">
       <c r="A17" t="s">
         <v>1235</v>
       </c>
@@ -9266,7 +9275,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="60" customHeight="1">
       <c r="A18" t="s">
         <v>1242</v>
       </c>
@@ -9289,7 +9298,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="45" customHeight="1">
       <c r="A19" t="s">
         <v>1249</v>
       </c>
@@ -9312,7 +9321,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="60" customHeight="1">
       <c r="A20" t="s">
         <v>1256</v>
       </c>
@@ -9335,7 +9344,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="60" customHeight="1">
       <c r="A21" t="s">
         <v>1263</v>
       </c>
@@ -9358,7 +9367,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="60" customHeight="1">
       <c r="A22" t="s">
         <v>1270</v>
       </c>
@@ -9381,7 +9390,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="60" customHeight="1">
       <c r="A23" t="s">
         <v>1277</v>
       </c>
@@ -9404,7 +9413,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="60" customHeight="1">
       <c r="A24" t="s">
         <v>1284</v>
       </c>
@@ -9427,7 +9436,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="25" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="60" customHeight="1">
       <c r="A25" t="s">
         <v>1291</v>
       </c>
@@ -9450,7 +9459,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="60" customHeight="1">
       <c r="A26" t="s">
         <v>1298</v>
       </c>
@@ -9473,7 +9482,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="60" customHeight="1">
       <c r="A27" t="s">
         <v>1305</v>
       </c>
@@ -9505,15 +9514,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" customWidth="1"/>
     <col min="4" max="6" width="25" customWidth="1"/>
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="32.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>353</v>
       </c>
@@ -9536,7 +9545,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="45" customHeight="1">
       <c r="A2" t="s">
         <v>1312</v>
       </c>
@@ -9559,7 +9568,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="60" customHeight="1">
       <c r="A3" t="s">
         <v>1319</v>
       </c>
@@ -9582,7 +9591,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="60" customHeight="1">
       <c r="A4" t="s">
         <v>1326</v>
       </c>
@@ -9605,7 +9614,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="60" customHeight="1">
       <c r="A5" t="s">
         <v>1333</v>
       </c>
@@ -9628,7 +9637,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="60" customHeight="1">
       <c r="A6" t="s">
         <v>1340</v>
       </c>
@@ -9660,7 +9669,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
@@ -9668,7 +9677,7 @@
     <col min="7" max="7" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32.1" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="32.1" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>353</v>
       </c>
@@ -9691,7 +9700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="60" customHeight="1">
       <c r="A2" t="s">
         <v>1347</v>
       </c>
@@ -9714,7 +9723,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="60" customHeight="1">
       <c r="A3" t="s">
         <v>1354</v>
       </c>
@@ -9737,7 +9746,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="60" customHeight="1">
       <c r="A4" t="s">
         <v>1361</v>
       </c>
@@ -9760,7 +9769,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="60" customHeight="1">
       <c r="A5" t="s">
         <v>1368</v>
       </c>
@@ -9783,7 +9792,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="60" customHeight="1">
       <c r="A6" t="s">
         <v>1375</v>
       </c>
@@ -9806,7 +9815,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="60" customHeight="1">
       <c r="A7" t="s">
         <v>1382</v>
       </c>
@@ -9829,7 +9838,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="60" customHeight="1">
       <c r="A8" t="s">
         <v>1389</v>
       </c>
@@ -9852,7 +9861,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="60" customHeight="1">
       <c r="A9" t="s">
         <v>1396</v>
       </c>
@@ -9875,7 +9884,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="60" customHeight="1">
       <c r="A10" t="s">
         <v>1403</v>
       </c>
@@ -9898,7 +9907,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="45" customHeight="1">
       <c r="A11" t="s">
         <v>1410</v>
       </c>
@@ -9921,7 +9930,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="60" customHeight="1">
       <c r="A12" t="s">
         <v>1417</v>
       </c>
@@ -9944,7 +9953,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="60" customHeight="1">
       <c r="A13" t="s">
         <v>1424</v>
       </c>
@@ -9967,7 +9976,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="60" customHeight="1">
       <c r="A14" t="s">
         <v>1431</v>
       </c>
@@ -9990,7 +9999,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="60" customHeight="1">
       <c r="A15" t="s">
         <v>1438</v>
       </c>
@@ -10013,7 +10022,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="60" customHeight="1">
       <c r="A16" t="s">
         <v>1445</v>
       </c>
@@ -10036,7 +10045,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="17" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="60" customHeight="1">
       <c r="A17" t="s">
         <v>1452</v>
       </c>
@@ -10059,7 +10068,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="60" customHeight="1">
       <c r="A18" t="s">
         <v>1459</v>
       </c>
@@ -10082,7 +10091,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="60" customHeight="1">
       <c r="A19" t="s">
         <v>1466</v>
       </c>
@@ -10105,7 +10114,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="60" customHeight="1">
       <c r="A20" t="s">
         <v>1473</v>
       </c>
@@ -10128,7 +10137,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="21" ht="60" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="60" customHeight="1">
       <c r="A21" t="s">
         <v>1480</v>
       </c>
@@ -10159,8 +10168,8 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
